--- a/frontend/public/様式1_活動報告書_農地維持支払.xlsx
+++ b/frontend/public/様式1_活動報告書_農地維持支払.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taros\Documents\Koyu\dev\tamokuteki_kinouhakki_sokushin_erp\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C58B51-F81D-49CC-B8E2-D6CB57D58C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24FF0D2-BDD6-48EC-BCC9-C08B2B6EC905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="5400" windowWidth="21528" windowHeight="18600" xr2:uid="{F21A66FA-6EBE-4524-A7C7-D4EDBA8E7EA2}"/>
+    <workbookView xWindow="732" yWindow="3324" windowWidth="36360" windowHeight="18600" xr2:uid="{F21A66FA-6EBE-4524-A7C7-D4EDBA8E7EA2}"/>
   </bookViews>
   <sheets>
     <sheet name="活動報告書" sheetId="8" r:id="rId1"/>
@@ -1201,7 +1201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1268,9 +1268,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1278,80 +1275,173 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="38" fontId="0" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1361,102 +1451,51 @@
     <xf numFmtId="38" fontId="0" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1487,47 +1526,35 @@
     <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1540,36 +1567,6 @@
     </xf>
     <xf numFmtId="38" fontId="0" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1902,335 +1899,335 @@
       </c>
     </row>
     <row r="2" spans="1:37" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
     </row>
     <row r="3" spans="1:37" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="O3" s="26" t="s">
+      <c r="O3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26">
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24">
         <v>130</v>
       </c>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
-      <c r="W3" s="26" t="s">
+      <c r="S3" s="24"/>
+      <c r="T3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26" t="s">
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
       <c r="AK3" s="21"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26" t="s">
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="43" t="s">
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="26" t="s">
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
-      <c r="AI4" s="26"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
     </row>
     <row r="5" spans="1:37" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="26"/>
-      <c r="O5" s="34" t="s">
+      <c r="N5" s="24"/>
+      <c r="O5" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34" t="s">
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="34"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
     </row>
     <row r="6" spans="1:37" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="26"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
     </row>
     <row r="7" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41" t="s">
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26" t="s">
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="26">
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="70"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="72"/>
+      <c r="Y7" s="24">
         <v>1</v>
       </c>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="26"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
     </row>
     <row r="8" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="30"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="34"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="34"/>
+      <c r="AB8" s="34"/>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="34"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="34"/>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="35"/>
     </row>
     <row r="9" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="32"/>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="33"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="38"/>
     </row>
     <row r="10" spans="1:37" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="Y10" s="10" t="s">
@@ -2238,26 +2235,26 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="34" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="35" t="s">
+      <c r="L11" s="24"/>
+      <c r="M11" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="N11" s="36"/>
+      <c r="N11" s="40"/>
       <c r="Y11" s="10" t="s">
         <v>28</v>
       </c>
@@ -2266,21 +2263,21 @@
       <c r="A12" s="19">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
       <c r="Y12" s="10" t="s">
         <v>29</v>
       </c>
@@ -2289,23 +2286,23 @@
       <c r="A13" s="19">
         <v>2</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="27" t="s">
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
       <c r="Y13" s="10" t="s">
         <v>30</v>
       </c>
@@ -2314,42 +2311,42 @@
       <c r="A14" s="19">
         <v>3</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="26"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
     </row>
     <row r="15" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="19">
         <v>4</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="W15" s="23" t="s">
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="W15" s="22" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2357,75 +2354,74 @@
       <c r="A16" s="19">
         <v>5</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="W16" s="26"/>
-      <c r="X16" s="26"/>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="26"/>
-      <c r="AB16" s="26"/>
-      <c r="AC16" s="26"/>
-      <c r="AD16" s="26"/>
-      <c r="AE16" s="26"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="26"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="24"/>
     </row>
     <row r="17" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="26"/>
-      <c r="AD17" s="26"/>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="26"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
+      <c r="AH17" s="24"/>
     </row>
     <row r="18" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="S4:X6"/>
-    <mergeCell ref="Y4:Z6"/>
-    <mergeCell ref="AA4:AI6"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="M5:N6"/>
-    <mergeCell ref="O5:P6"/>
-    <mergeCell ref="Q5:R6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="W3:AD3"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+  <mergeCells count="54">
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="AF16:AH17"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="AC16:AE17"/>
+    <mergeCell ref="Z16:AB17"/>
+    <mergeCell ref="W16:Y17"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="AA7:AI7"/>
@@ -2440,25 +2436,27 @@
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="O7:P7"/>
-    <mergeCell ref="AF16:AH17"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="AC16:AE17"/>
-    <mergeCell ref="Z16:AB17"/>
-    <mergeCell ref="W16:Y17"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="S7:X7"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="W3:AD3"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="S4:X6"/>
+    <mergeCell ref="Y4:Z6"/>
+    <mergeCell ref="AA4:AI6"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="O5:P6"/>
+    <mergeCell ref="Q5:R6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="I6:L6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2485,1100 +2483,1100 @@
       <c r="A1" t="s">
         <v>45</v>
       </c>
-      <c r="AM1" s="24" t="s">
+      <c r="AM1" s="23" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71"/>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="71"/>
-      <c r="AH2" s="71"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="71"/>
-      <c r="AK2" s="71"/>
-      <c r="AL2" s="71"/>
-      <c r="AM2" s="71"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="57"/>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="57"/>
+      <c r="AL2" s="57"/>
+      <c r="AM2" s="57"/>
     </row>
     <row r="3" spans="1:39" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="Q3" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="72" t="str">
+      <c r="Q3" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="58" t="str">
         <f>IF(活動報告書!W3="","",活動報告書!W3)</f>
         <v>鎌田緑保護会</v>
       </c>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="55" t="s">
+      <c r="V3" s="58"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="58"/>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="56"/>
-      <c r="AH3" s="56"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="73" t="str">
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="61"/>
+      <c r="AJ3" s="62" t="str">
         <f>IF(活動報告書!A7="","",活動報告書!A7)</f>
         <v/>
       </c>
-      <c r="AK3" s="73"/>
-      <c r="AL3" s="74"/>
-      <c r="AM3" s="74"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="63"/>
+      <c r="AM3" s="63"/>
     </row>
     <row r="4" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="49" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="55" t="s">
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="57"/>
-      <c r="AJ4" s="75" t="s">
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="60"/>
+      <c r="AB4" s="60"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="60"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
+      <c r="AK4" s="64"/>
+      <c r="AL4" s="64"/>
+      <c r="AM4" s="64"/>
     </row>
     <row r="5" spans="1:39" s="10" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="76" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="81" t="s">
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="34" t="s">
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="Y5" s="34"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34" t="s">
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="76" t="s">
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="AG5" s="77"/>
-      <c r="AH5" s="78"/>
-      <c r="AI5" s="79"/>
-      <c r="AJ5" s="75"/>
-      <c r="AK5" s="75"/>
-      <c r="AL5" s="75"/>
-      <c r="AM5" s="75"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="64"/>
+      <c r="AK5" s="64"/>
+      <c r="AL5" s="64"/>
+      <c r="AM5" s="64"/>
     </row>
     <row r="6" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="58">
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="48">
         <f t="shared" ref="O6:O22" si="0">G6*L6</f>
         <v>0</v>
       </c>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="59"/>
-      <c r="R6" s="60"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="53"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="49"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="67"/>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="58">
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="52"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="54"/>
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="48">
         <f t="shared" ref="AF6:AF22" si="1">X6*AC6</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="59"/>
-      <c r="AI6" s="60"/>
-      <c r="AJ6" s="61">
+      <c r="AG6" s="49"/>
+      <c r="AH6" s="49"/>
+      <c r="AI6" s="50"/>
+      <c r="AJ6" s="74">
         <f>O6+AF6</f>
         <v>0</v>
       </c>
-      <c r="AK6" s="61"/>
-      <c r="AL6" s="61"/>
-      <c r="AM6" s="61"/>
+      <c r="AK6" s="74"/>
+      <c r="AL6" s="74"/>
+      <c r="AM6" s="74"/>
     </row>
     <row r="7" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="58">
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="57"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="67"/>
-      <c r="AD7" s="67"/>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="58">
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="59"/>
-      <c r="AH7" s="59"/>
-      <c r="AI7" s="60"/>
-      <c r="AJ7" s="61">
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="74">
         <f t="shared" ref="AJ7:AJ22" si="2">O7+AF7</f>
         <v>0</v>
       </c>
-      <c r="AK7" s="61"/>
-      <c r="AL7" s="61"/>
-      <c r="AM7" s="61"/>
+      <c r="AK7" s="74"/>
+      <c r="AL7" s="74"/>
+      <c r="AM7" s="74"/>
     </row>
     <row r="8" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
+      <c r="A8" s="55"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="58">
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="60"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="53"/>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="49"/>
-      <c r="AB8" s="49"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="62"/>
-      <c r="AE8" s="62"/>
-      <c r="AF8" s="58">
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="77"/>
+      <c r="T8" s="78"/>
+      <c r="U8" s="78"/>
+      <c r="V8" s="78"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="76"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG8" s="59"/>
-      <c r="AH8" s="59"/>
-      <c r="AI8" s="60"/>
-      <c r="AJ8" s="61">
+      <c r="AG8" s="49"/>
+      <c r="AH8" s="49"/>
+      <c r="AI8" s="50"/>
+      <c r="AJ8" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK8" s="61"/>
-      <c r="AL8" s="61"/>
-      <c r="AM8" s="61"/>
+      <c r="AK8" s="74"/>
+      <c r="AL8" s="74"/>
+      <c r="AM8" s="74"/>
     </row>
     <row r="9" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="49"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
+      <c r="A9" s="55"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="58">
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="60"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="58">
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="59"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
+      <c r="AC9" s="55"/>
+      <c r="AD9" s="55"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG9" s="59"/>
-      <c r="AH9" s="59"/>
-      <c r="AI9" s="60"/>
-      <c r="AJ9" s="61">
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="50"/>
+      <c r="AJ9" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK9" s="61"/>
-      <c r="AL9" s="61"/>
-      <c r="AM9" s="61"/>
+      <c r="AK9" s="74"/>
+      <c r="AL9" s="74"/>
+      <c r="AM9" s="74"/>
     </row>
     <row r="10" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="58">
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="60"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="58">
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="55"/>
+      <c r="Y10" s="55"/>
+      <c r="Z10" s="55"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="55"/>
+      <c r="AC10" s="55"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="59"/>
-      <c r="AH10" s="59"/>
-      <c r="AI10" s="60"/>
-      <c r="AJ10" s="61">
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="50"/>
+      <c r="AJ10" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="61"/>
-      <c r="AL10" s="61"/>
-      <c r="AM10" s="61"/>
+      <c r="AK10" s="74"/>
+      <c r="AL10" s="74"/>
+      <c r="AM10" s="74"/>
     </row>
     <row r="11" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="49"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="58">
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="60"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="49"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="58">
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="59"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="55"/>
+      <c r="AC11" s="55"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="59"/>
-      <c r="AH11" s="59"/>
-      <c r="AI11" s="60"/>
-      <c r="AJ11" s="61">
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="61"/>
-      <c r="AL11" s="61"/>
-      <c r="AM11" s="61"/>
+      <c r="AK11" s="74"/>
+      <c r="AL11" s="74"/>
+      <c r="AM11" s="74"/>
     </row>
     <row r="12" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="49"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="58">
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="59"/>
-      <c r="R12" s="60"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="58">
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="59"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="55"/>
+      <c r="AC12" s="55"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="59"/>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="60"/>
-      <c r="AJ12" s="61">
+      <c r="AG12" s="49"/>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="61"/>
-      <c r="AL12" s="61"/>
-      <c r="AM12" s="61"/>
+      <c r="AK12" s="74"/>
+      <c r="AL12" s="74"/>
+      <c r="AM12" s="74"/>
     </row>
     <row r="13" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="58">
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="60"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="58">
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="61"/>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="55"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="55"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="60"/>
-      <c r="AJ13" s="61">
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="50"/>
+      <c r="AJ13" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="61"/>
-      <c r="AL13" s="61"/>
-      <c r="AM13" s="61"/>
+      <c r="AK13" s="74"/>
+      <c r="AL13" s="74"/>
+      <c r="AM13" s="74"/>
     </row>
     <row r="14" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="49"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="58">
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="49"/>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="49"/>
-      <c r="AA14" s="49"/>
-      <c r="AB14" s="49"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="58">
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="55"/>
+      <c r="Y14" s="55"/>
+      <c r="Z14" s="55"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="55"/>
+      <c r="AC14" s="55"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="55"/>
+      <c r="AF14" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="59"/>
-      <c r="AH14" s="59"/>
-      <c r="AI14" s="60"/>
-      <c r="AJ14" s="61">
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="49"/>
+      <c r="AI14" s="50"/>
+      <c r="AJ14" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="61"/>
-      <c r="AL14" s="61"/>
-      <c r="AM14" s="61"/>
+      <c r="AK14" s="74"/>
+      <c r="AL14" s="74"/>
+      <c r="AM14" s="74"/>
     </row>
     <row r="15" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="49"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="58">
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="57"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="49"/>
-      <c r="AB15" s="49"/>
-      <c r="AC15" s="49"/>
-      <c r="AD15" s="49"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="58">
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="59"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="60"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="55"/>
+      <c r="Y15" s="55"/>
+      <c r="Z15" s="55"/>
+      <c r="AA15" s="55"/>
+      <c r="AB15" s="55"/>
+      <c r="AC15" s="55"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="55"/>
+      <c r="AF15" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="59"/>
-      <c r="AH15" s="59"/>
-      <c r="AI15" s="60"/>
-      <c r="AJ15" s="61">
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="50"/>
+      <c r="AJ15" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="61"/>
-      <c r="AL15" s="61"/>
-      <c r="AM15" s="61"/>
+      <c r="AK15" s="74"/>
+      <c r="AL15" s="74"/>
+      <c r="AM15" s="74"/>
     </row>
     <row r="16" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="58">
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="59"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="49"/>
-      <c r="AA16" s="49"/>
-      <c r="AB16" s="49"/>
-      <c r="AC16" s="49"/>
-      <c r="AD16" s="49"/>
-      <c r="AE16" s="49"/>
-      <c r="AF16" s="58">
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="59"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="61"/>
+      <c r="X16" s="55"/>
+      <c r="Y16" s="55"/>
+      <c r="Z16" s="55"/>
+      <c r="AA16" s="55"/>
+      <c r="AB16" s="55"/>
+      <c r="AC16" s="55"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="55"/>
+      <c r="AF16" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="59"/>
-      <c r="AH16" s="59"/>
-      <c r="AI16" s="60"/>
-      <c r="AJ16" s="61">
+      <c r="AG16" s="49"/>
+      <c r="AH16" s="49"/>
+      <c r="AI16" s="50"/>
+      <c r="AJ16" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="61"/>
-      <c r="AL16" s="61"/>
-      <c r="AM16" s="61"/>
+      <c r="AK16" s="74"/>
+      <c r="AL16" s="74"/>
+      <c r="AM16" s="74"/>
     </row>
     <row r="17" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="58">
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="59"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="57"/>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="49"/>
-      <c r="AA17" s="49"/>
-      <c r="AB17" s="49"/>
-      <c r="AC17" s="49"/>
-      <c r="AD17" s="49"/>
-      <c r="AE17" s="49"/>
-      <c r="AF17" s="58">
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="55"/>
+      <c r="Y17" s="55"/>
+      <c r="Z17" s="55"/>
+      <c r="AA17" s="55"/>
+      <c r="AB17" s="55"/>
+      <c r="AC17" s="55"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="55"/>
+      <c r="AF17" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="59"/>
-      <c r="AH17" s="59"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="61">
+      <c r="AG17" s="49"/>
+      <c r="AH17" s="49"/>
+      <c r="AI17" s="50"/>
+      <c r="AJ17" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="61"/>
-      <c r="AL17" s="61"/>
-      <c r="AM17" s="61"/>
+      <c r="AK17" s="74"/>
+      <c r="AL17" s="74"/>
+      <c r="AM17" s="74"/>
     </row>
     <row r="18" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="58">
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="49"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="49"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="58">
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
+      <c r="R18" s="50"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="61"/>
+      <c r="X18" s="55"/>
+      <c r="Y18" s="55"/>
+      <c r="Z18" s="55"/>
+      <c r="AA18" s="55"/>
+      <c r="AB18" s="55"/>
+      <c r="AC18" s="55"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="55"/>
+      <c r="AF18" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="59"/>
-      <c r="AH18" s="59"/>
-      <c r="AI18" s="60"/>
-      <c r="AJ18" s="61">
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="50"/>
+      <c r="AJ18" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="61"/>
-      <c r="AL18" s="61"/>
-      <c r="AM18" s="61"/>
+      <c r="AK18" s="74"/>
+      <c r="AL18" s="74"/>
+      <c r="AM18" s="74"/>
     </row>
     <row r="19" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="58">
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="59"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="49"/>
-      <c r="AA19" s="49"/>
-      <c r="AB19" s="49"/>
-      <c r="AC19" s="49"/>
-      <c r="AD19" s="49"/>
-      <c r="AE19" s="49"/>
-      <c r="AF19" s="58">
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="59"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="55"/>
+      <c r="Y19" s="55"/>
+      <c r="Z19" s="55"/>
+      <c r="AA19" s="55"/>
+      <c r="AB19" s="55"/>
+      <c r="AC19" s="55"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="55"/>
+      <c r="AF19" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="59"/>
-      <c r="AH19" s="59"/>
-      <c r="AI19" s="60"/>
-      <c r="AJ19" s="61">
+      <c r="AG19" s="49"/>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="50"/>
+      <c r="AJ19" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="61"/>
-      <c r="AL19" s="61"/>
-      <c r="AM19" s="61"/>
+      <c r="AK19" s="74"/>
+      <c r="AL19" s="74"/>
+      <c r="AM19" s="74"/>
     </row>
     <row r="20" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="58">
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="49"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="49"/>
-      <c r="AC20" s="49"/>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="58">
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="55"/>
+      <c r="Y20" s="55"/>
+      <c r="Z20" s="55"/>
+      <c r="AA20" s="55"/>
+      <c r="AB20" s="55"/>
+      <c r="AC20" s="55"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="55"/>
+      <c r="AF20" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="59"/>
-      <c r="AH20" s="59"/>
-      <c r="AI20" s="60"/>
-      <c r="AJ20" s="61">
+      <c r="AG20" s="49"/>
+      <c r="AH20" s="49"/>
+      <c r="AI20" s="50"/>
+      <c r="AJ20" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="61"/>
-      <c r="AL20" s="61"/>
-      <c r="AM20" s="61"/>
+      <c r="AK20" s="74"/>
+      <c r="AL20" s="74"/>
+      <c r="AM20" s="74"/>
     </row>
     <row r="21" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="58">
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="56"/>
-      <c r="U21" s="56"/>
-      <c r="V21" s="56"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="49"/>
-      <c r="Z21" s="49"/>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="49"/>
-      <c r="AF21" s="58">
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="55"/>
+      <c r="Y21" s="55"/>
+      <c r="Z21" s="55"/>
+      <c r="AA21" s="55"/>
+      <c r="AB21" s="55"/>
+      <c r="AC21" s="55"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="55"/>
+      <c r="AF21" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="59"/>
-      <c r="AH21" s="59"/>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="61">
+      <c r="AG21" s="49"/>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="50"/>
+      <c r="AJ21" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="61"/>
-      <c r="AL21" s="61"/>
-      <c r="AM21" s="61"/>
+      <c r="AK21" s="74"/>
+      <c r="AL21" s="74"/>
+      <c r="AM21" s="74"/>
     </row>
     <row r="22" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="58">
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="48">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="59"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="56"/>
-      <c r="U22" s="56"/>
-      <c r="V22" s="56"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="49"/>
-      <c r="Y22" s="49"/>
-      <c r="Z22" s="49"/>
-      <c r="AA22" s="49"/>
-      <c r="AB22" s="49"/>
-      <c r="AC22" s="49"/>
-      <c r="AD22" s="49"/>
-      <c r="AE22" s="49"/>
-      <c r="AF22" s="58">
+      <c r="P22" s="49"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="55"/>
+      <c r="Z22" s="55"/>
+      <c r="AA22" s="55"/>
+      <c r="AB22" s="55"/>
+      <c r="AC22" s="55"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="55"/>
+      <c r="AF22" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="59"/>
-      <c r="AH22" s="59"/>
-      <c r="AI22" s="60"/>
-      <c r="AJ22" s="61">
+      <c r="AG22" s="49"/>
+      <c r="AH22" s="49"/>
+      <c r="AI22" s="50"/>
+      <c r="AJ22" s="74">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="61"/>
-      <c r="AL22" s="61"/>
-      <c r="AM22" s="61"/>
+      <c r="AK22" s="74"/>
+      <c r="AL22" s="74"/>
+      <c r="AM22" s="74"/>
     </row>
     <row r="23" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="53">
+      <c r="G23" s="54">
         <f>SUM(G6:G22)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="50">
+      <c r="H23" s="54"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="80">
         <f>SUM(O6:O22)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="52"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
-      <c r="Z23" s="49"/>
-      <c r="AA23" s="49"/>
-      <c r="AB23" s="49"/>
-      <c r="AC23" s="49"/>
-      <c r="AD23" s="49"/>
-      <c r="AE23" s="49"/>
-      <c r="AF23" s="50">
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="55"/>
+      <c r="Y23" s="55"/>
+      <c r="Z23" s="55"/>
+      <c r="AA23" s="55"/>
+      <c r="AB23" s="55"/>
+      <c r="AC23" s="55"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="55"/>
+      <c r="AF23" s="80">
         <f>SUM(AF6:AF22)</f>
         <v>0</v>
       </c>
-      <c r="AG23" s="51"/>
-      <c r="AH23" s="51"/>
-      <c r="AI23" s="52"/>
-      <c r="AJ23" s="50">
+      <c r="AG23" s="81"/>
+      <c r="AH23" s="81"/>
+      <c r="AI23" s="82"/>
+      <c r="AJ23" s="80">
         <f>SUM(AJ6:AJ22)</f>
         <v>0</v>
       </c>
-      <c r="AK23" s="51"/>
-      <c r="AL23" s="51"/>
-      <c r="AM23" s="52"/>
+      <c r="AK23" s="81"/>
+      <c r="AL23" s="81"/>
+      <c r="AM23" s="82"/>
     </row>
     <row r="24" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9" t="s">
@@ -3898,28 +3896,175 @@
     </row>
   </sheetData>
   <mergeCells count="215">
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="S6:W6"/>
-    <mergeCell ref="X6:Z6"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:AD3"/>
-    <mergeCell ref="AE3:AI3"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:R4"/>
-    <mergeCell ref="S4:AI4"/>
-    <mergeCell ref="AJ4:AM5"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="AF5:AI5"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:W5"/>
-    <mergeCell ref="X5:AB5"/>
-    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="S22:W22"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="AJ22:AM22"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="AJ21:AM21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S20:W20"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AM20"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AM19"/>
+    <mergeCell ref="S19:W19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S18:W18"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AM18"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AM17"/>
+    <mergeCell ref="S17:W17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AM16"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AM15"/>
+    <mergeCell ref="S15:W15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AM14"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="S13:W13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="S12:W12"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AM9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AJ8:AM8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X8:Z8"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="J10:K10"/>
@@ -3944,175 +4089,28 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:N6"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AJ8:AM8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AM9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="S12:W12"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="S14:W14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AM14"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="S13:W13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="S16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AM16"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AM15"/>
-    <mergeCell ref="S15:W15"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S18:W18"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AM18"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AM17"/>
-    <mergeCell ref="S17:W17"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S20:W20"/>
-    <mergeCell ref="X20:Z20"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AM20"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AM19"/>
-    <mergeCell ref="S19:W19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="S22:W22"/>
-    <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="AJ22:AM22"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AC21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="AJ21:AM21"/>
-    <mergeCell ref="S21:W21"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="AJ23:AM23"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:W6"/>
+    <mergeCell ref="X6:Z6"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:AD3"/>
+    <mergeCell ref="AE3:AI3"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:R4"/>
+    <mergeCell ref="S4:AI4"/>
+    <mergeCell ref="AJ4:AM5"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="AF5:AI5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="X5:AB5"/>
+    <mergeCell ref="AC5:AE5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -4143,21 +4141,21 @@
       <c r="I1" s="12"/>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
-      <c r="L1" s="85" t="s">
+      <c r="L1" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="86"/>
-      <c r="U1" s="86"/>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+      <c r="W1" s="99"/>
+      <c r="X1" s="99"/>
       <c r="Y1" s="12"/>
       <c r="Z1" s="12"/>
       <c r="AA1" s="12"/>
@@ -4173,43 +4171,43 @@
       </c>
     </row>
     <row r="2" spans="1:37" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="108"/>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="108"/>
-      <c r="AH2" s="108"/>
-      <c r="AI2" s="108"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="83"/>
+      <c r="Y2" s="83"/>
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="83"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="83"/>
+      <c r="AD2" s="83"/>
+      <c r="AE2" s="83"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
+      <c r="AH2" s="83"/>
+      <c r="AI2" s="83"/>
     </row>
     <row r="3" spans="1:37" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="12"/>
@@ -4240,25 +4238,25 @@
       </c>
       <c r="U3" s="84"/>
       <c r="V3" s="84"/>
-      <c r="W3" s="49" t="s">
+      <c r="W3" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
+      <c r="X3" s="55"/>
+      <c r="Y3" s="55"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
       <c r="AE3" s="84" t="s">
         <v>43</v>
       </c>
       <c r="AF3" s="84"/>
       <c r="AG3" s="84"/>
-      <c r="AH3" s="49">
+      <c r="AH3" s="55">
         <v>1</v>
       </c>
-      <c r="AI3" s="49"/>
+      <c r="AI3" s="55"/>
       <c r="AK3" s="1"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.45">
@@ -4292,10 +4290,10 @@
       <c r="V4" s="84"/>
       <c r="W4" s="84"/>
       <c r="X4" s="84"/>
-      <c r="Y4" s="102" t="s">
+      <c r="Y4" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="Z4" s="103"/>
+      <c r="Z4" s="86"/>
       <c r="AA4" s="84" t="s">
         <v>8</v>
       </c>
@@ -4329,22 +4327,22 @@
         <v>4</v>
       </c>
       <c r="N5" s="84"/>
-      <c r="O5" s="99" t="s">
+      <c r="O5" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99" t="s">
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="99"/>
+      <c r="R5" s="91"/>
       <c r="S5" s="84"/>
       <c r="T5" s="84"/>
       <c r="U5" s="84"/>
       <c r="V5" s="84"/>
       <c r="W5" s="84"/>
       <c r="X5" s="84"/>
-      <c r="Y5" s="104"/>
-      <c r="Z5" s="105"/>
+      <c r="Y5" s="87"/>
+      <c r="Z5" s="88"/>
       <c r="AA5" s="84"/>
       <c r="AB5" s="84"/>
       <c r="AC5" s="84"/>
@@ -4376,18 +4374,18 @@
       <c r="L6" s="84"/>
       <c r="M6" s="84"/>
       <c r="N6" s="84"/>
-      <c r="O6" s="99"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="99"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
       <c r="S6" s="84"/>
       <c r="T6" s="84"/>
       <c r="U6" s="84"/>
       <c r="V6" s="84"/>
       <c r="W6" s="84"/>
       <c r="X6" s="84"/>
-      <c r="Y6" s="106"/>
-      <c r="Z6" s="107"/>
+      <c r="Y6" s="89"/>
+      <c r="Z6" s="90"/>
       <c r="AA6" s="84"/>
       <c r="AB6" s="84"/>
       <c r="AC6" s="84"/>
@@ -4399,40 +4397,40 @@
       <c r="AI6" s="84"/>
     </row>
     <row r="7" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="94">
+      <c r="A7" s="107">
         <v>46183</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95">
+      <c r="B7" s="107"/>
+      <c r="C7" s="92">
         <v>0.375</v>
       </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95">
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92">
         <v>0.45833333333333331</v>
       </c>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
-      <c r="I7" s="53">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="54">
         <v>2</v>
       </c>
-      <c r="J7" s="53"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="84" t="s">
         <v>11</v>
       </c>
       <c r="L7" s="84"/>
-      <c r="M7" s="49">
+      <c r="M7" s="55">
         <v>2</v>
       </c>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49">
+      <c r="N7" s="55"/>
+      <c r="O7" s="55">
         <v>2</v>
       </c>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="49">
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55">
         <v>4</v>
       </c>
-      <c r="R7" s="49"/>
+      <c r="R7" s="55"/>
       <c r="S7" s="2">
         <v>7</v>
       </c>
@@ -4443,97 +4441,97 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="49">
+      <c r="Y7" s="55">
         <v>1</v>
       </c>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="87" t="s">
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="AB7" s="87"/>
-      <c r="AC7" s="87"/>
-      <c r="AD7" s="87"/>
-      <c r="AE7" s="87"/>
-      <c r="AF7" s="87"/>
-      <c r="AG7" s="87"/>
-      <c r="AH7" s="87"/>
-      <c r="AI7" s="87"/>
+      <c r="AB7" s="100"/>
+      <c r="AC7" s="100"/>
+      <c r="AD7" s="100"/>
+      <c r="AE7" s="100"/>
+      <c r="AF7" s="100"/>
+      <c r="AG7" s="100"/>
+      <c r="AH7" s="100"/>
+      <c r="AI7" s="100"/>
     </row>
     <row r="8" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="89"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="89"/>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="89"/>
-      <c r="L8" s="89"/>
-      <c r="M8" s="89"/>
-      <c r="N8" s="89"/>
-      <c r="O8" s="89"/>
-      <c r="P8" s="89"/>
-      <c r="Q8" s="89"/>
-      <c r="R8" s="89"/>
-      <c r="S8" s="89"/>
-      <c r="T8" s="89"/>
-      <c r="U8" s="89"/>
-      <c r="V8" s="89"/>
-      <c r="W8" s="89"/>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
-      <c r="Z8" s="89"/>
-      <c r="AA8" s="89"/>
-      <c r="AB8" s="89"/>
-      <c r="AC8" s="89"/>
-      <c r="AD8" s="89"/>
-      <c r="AE8" s="89"/>
-      <c r="AF8" s="89"/>
-      <c r="AG8" s="89"/>
-      <c r="AH8" s="89"/>
-      <c r="AI8" s="90"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
+      <c r="J8" s="102"/>
+      <c r="K8" s="102"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="102"/>
+      <c r="N8" s="102"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102"/>
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="102"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="102"/>
+      <c r="AE8" s="102"/>
+      <c r="AF8" s="102"/>
+      <c r="AG8" s="102"/>
+      <c r="AH8" s="102"/>
+      <c r="AI8" s="103"/>
     </row>
     <row r="9" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="92"/>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="92"/>
-      <c r="R9" s="92"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="92"/>
-      <c r="U9" s="92"/>
-      <c r="V9" s="92"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="92"/>
-      <c r="Y9" s="92"/>
-      <c r="Z9" s="92"/>
-      <c r="AA9" s="92"/>
-      <c r="AB9" s="92"/>
-      <c r="AC9" s="92"/>
-      <c r="AD9" s="92"/>
-      <c r="AE9" s="92"/>
-      <c r="AF9" s="92"/>
-      <c r="AG9" s="92"/>
-      <c r="AH9" s="92"/>
-      <c r="AI9" s="93"/>
+      <c r="A9" s="104"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="105"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+      <c r="AC9" s="105"/>
+      <c r="AD9" s="105"/>
+      <c r="AE9" s="105"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="105"/>
+      <c r="AH9" s="105"/>
+      <c r="AI9" s="106"/>
     </row>
     <row r="10" spans="1:37" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12"/>
@@ -4587,14 +4585,14 @@
       <c r="H11" s="84"/>
       <c r="I11" s="84"/>
       <c r="J11" s="84"/>
-      <c r="K11" s="99" t="s">
+      <c r="K11" s="91" t="s">
         <v>58</v>
       </c>
       <c r="L11" s="84"/>
-      <c r="M11" s="100" t="s">
+      <c r="M11" s="93" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="101"/>
+      <c r="N11" s="94"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
@@ -4623,21 +4621,21 @@
       <c r="A12" s="14">
         <v>1</v>
       </c>
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="96"/>
-      <c r="K12" s="97" t="s">
+      <c r="C12" s="95"/>
+      <c r="D12" s="95"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="95"/>
+      <c r="K12" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="L12" s="98"/>
+      <c r="L12" s="97"/>
       <c r="M12" s="84"/>
       <c r="N12" s="84"/>
       <c r="O12" s="12"/>
@@ -4668,21 +4666,21 @@
       <c r="A13" s="14">
         <v>2</v>
       </c>
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="96"/>
-      <c r="K13" s="97" t="s">
+      <c r="C13" s="95"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="L13" s="98"/>
+      <c r="L13" s="97"/>
       <c r="M13" s="84"/>
       <c r="N13" s="84"/>
       <c r="O13" s="12"/>
@@ -4713,19 +4711,19 @@
       <c r="A14" s="14">
         <v>3</v>
       </c>
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="96"/>
-      <c r="D14" s="96"/>
-      <c r="E14" s="96"/>
-      <c r="F14" s="96"/>
-      <c r="G14" s="96"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="96"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="57"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="61"/>
       <c r="M14" s="84"/>
       <c r="N14" s="84"/>
       <c r="O14" s="12"/>
@@ -4754,21 +4752,21 @@
       <c r="A15" s="14">
         <v>4</v>
       </c>
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="97" t="s">
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="98"/>
+      <c r="L15" s="97"/>
       <c r="M15" s="84"/>
       <c r="N15" s="84"/>
       <c r="O15" s="12"/>
@@ -4799,17 +4797,17 @@
       <c r="A16" s="14">
         <v>5</v>
       </c>
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="96"/>
-      <c r="I16" s="96"/>
-      <c r="J16" s="96"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="95"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="95"/>
       <c r="K16" s="84"/>
       <c r="L16" s="84"/>
       <c r="M16" s="84"/>
@@ -4879,44 +4877,6 @@
     <row r="19" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A2:AI2"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:V3"/>
-    <mergeCell ref="W3:AD3"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="S4:X6"/>
-    <mergeCell ref="Y4:Z6"/>
-    <mergeCell ref="AA4:AI6"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="M5:N6"/>
-    <mergeCell ref="O5:P6"/>
-    <mergeCell ref="Q5:R6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="M4:R4"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="B15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
     <mergeCell ref="W16:Y17"/>
     <mergeCell ref="Z16:AB17"/>
     <mergeCell ref="AC16:AE17"/>
@@ -4933,6 +4893,44 @@
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:E7"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="M4:R4"/>
+    <mergeCell ref="S4:X6"/>
+    <mergeCell ref="Y4:Z6"/>
+    <mergeCell ref="AA4:AI6"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="O5:P6"/>
+    <mergeCell ref="Q5:R6"/>
+    <mergeCell ref="A2:AI2"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:V3"/>
+    <mergeCell ref="W3:AD3"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -4956,1172 +4954,1172 @@
       <c r="A1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="109" t="s">
+      <c r="M1" s="118" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
+      <c r="Y1" s="118"/>
+      <c r="Z1" s="118"/>
       <c r="AM1" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="71" t="s">
+      <c r="A2" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
-      <c r="Y2" s="71"/>
-      <c r="Z2" s="71"/>
-      <c r="AA2" s="71"/>
-      <c r="AB2" s="71"/>
-      <c r="AC2" s="71"/>
-      <c r="AD2" s="71"/>
-      <c r="AE2" s="71"/>
-      <c r="AF2" s="71"/>
-      <c r="AG2" s="71"/>
-      <c r="AH2" s="71"/>
-      <c r="AI2" s="71"/>
-      <c r="AJ2" s="71"/>
-      <c r="AK2" s="71"/>
-      <c r="AL2" s="71"/>
-      <c r="AM2" s="71"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="57"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="57"/>
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="57"/>
+      <c r="AL2" s="57"/>
+      <c r="AM2" s="57"/>
     </row>
     <row r="3" spans="1:39" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="Q3" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="72" t="str">
+      <c r="Q3" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="58" t="str">
         <f>IF(活動報告書_記載例!W3="","",活動報告書_記載例!W3)</f>
         <v>鯖石保全会</v>
       </c>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="55" t="s">
+      <c r="V3" s="58"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="58"/>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="56"/>
-      <c r="AH3" s="56"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="73">
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="61"/>
+      <c r="AJ3" s="62">
         <f>IF(活動報告書_記載例!A7="","",活動報告書_記載例!A7)</f>
         <v>46183</v>
       </c>
-      <c r="AK3" s="73"/>
-      <c r="AL3" s="74"/>
-      <c r="AM3" s="74"/>
+      <c r="AK3" s="62"/>
+      <c r="AL3" s="63"/>
+      <c r="AM3" s="63"/>
     </row>
     <row r="4" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="49" t="s">
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="49"/>
-      <c r="O4" s="49"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="55" t="s">
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
+      <c r="Q4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="57"/>
-      <c r="AJ4" s="117" t="s">
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="60"/>
+      <c r="AB4" s="60"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="60"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="61"/>
+      <c r="AJ4" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="117"/>
-      <c r="AL4" s="117"/>
-      <c r="AM4" s="117"/>
+      <c r="AK4" s="111"/>
+      <c r="AL4" s="111"/>
+      <c r="AM4" s="111"/>
     </row>
     <row r="5" spans="1:39" s="10" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="118" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="112" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="81" t="s">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="116"/>
+      <c r="S5" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="34" t="s">
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="Y5" s="34"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34" t="s">
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="31"/>
+      <c r="AC5" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="26"/>
-      <c r="AF5" s="118" t="s">
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="AG5" s="119"/>
-      <c r="AH5" s="120"/>
-      <c r="AI5" s="121"/>
-      <c r="AJ5" s="117"/>
-      <c r="AK5" s="117"/>
-      <c r="AL5" s="117"/>
-      <c r="AM5" s="117"/>
+      <c r="AG5" s="113"/>
+      <c r="AH5" s="114"/>
+      <c r="AI5" s="115"/>
+      <c r="AJ5" s="111"/>
+      <c r="AK5" s="111"/>
+      <c r="AL5" s="111"/>
+      <c r="AM5" s="111"/>
     </row>
     <row r="6" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
       <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="53">
+      <c r="G6" s="54">
         <v>2</v>
       </c>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="49" t="s">
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="49"/>
-      <c r="L6" s="63">
+      <c r="K6" s="55"/>
+      <c r="L6" s="75">
         <v>1000</v>
       </c>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="113">
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="108">
         <f t="shared" ref="O6:O22" si="0">G6*L6</f>
         <v>2000</v>
       </c>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="115"/>
-      <c r="S6" s="68" t="s">
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="53">
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="52"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="54">
         <v>2</v>
       </c>
-      <c r="Y6" s="53"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="49" t="s">
+      <c r="Y6" s="54"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="67">
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="56">
         <v>900</v>
       </c>
-      <c r="AD6" s="67"/>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="113">
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="108">
         <f t="shared" ref="AF6:AF22" si="1">X6*AC6</f>
         <v>1800</v>
       </c>
-      <c r="AG6" s="114"/>
-      <c r="AH6" s="114"/>
-      <c r="AI6" s="115"/>
-      <c r="AJ6" s="116">
+      <c r="AG6" s="109"/>
+      <c r="AH6" s="109"/>
+      <c r="AI6" s="110"/>
+      <c r="AJ6" s="117">
         <f>O6+AF6</f>
         <v>3800</v>
       </c>
-      <c r="AK6" s="116"/>
-      <c r="AL6" s="116"/>
-      <c r="AM6" s="116"/>
+      <c r="AK6" s="117"/>
+      <c r="AL6" s="117"/>
+      <c r="AM6" s="117"/>
     </row>
     <row r="7" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="54">
         <v>2</v>
       </c>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="49" t="s">
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="49"/>
-      <c r="L7" s="63">
+      <c r="K7" s="55"/>
+      <c r="L7" s="75">
         <v>1000</v>
       </c>
-      <c r="M7" s="63"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="113">
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="108">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P7" s="114"/>
-      <c r="Q7" s="114"/>
-      <c r="R7" s="115"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="57"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="67"/>
-      <c r="AD7" s="67"/>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="113">
+      <c r="P7" s="109"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="55"/>
+      <c r="Y7" s="55"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="55"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="114"/>
-      <c r="AH7" s="114"/>
-      <c r="AI7" s="115"/>
-      <c r="AJ7" s="116">
+      <c r="AG7" s="109"/>
+      <c r="AH7" s="109"/>
+      <c r="AI7" s="110"/>
+      <c r="AJ7" s="117">
         <f t="shared" ref="AJ7:AJ22" si="2">O7+AF7</f>
         <v>2000</v>
       </c>
-      <c r="AK7" s="116"/>
-      <c r="AL7" s="116"/>
-      <c r="AM7" s="116"/>
+      <c r="AK7" s="117"/>
+      <c r="AL7" s="117"/>
+      <c r="AM7" s="117"/>
     </row>
     <row r="8" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="54">
         <v>2</v>
       </c>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="49" t="s">
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="63">
+      <c r="K8" s="55"/>
+      <c r="L8" s="75">
         <v>1000</v>
       </c>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="113">
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="108">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="115"/>
-      <c r="S8" s="64" t="s">
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="110"/>
+      <c r="S8" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="66"/>
-      <c r="X8" s="53">
+      <c r="T8" s="78"/>
+      <c r="U8" s="78"/>
+      <c r="V8" s="78"/>
+      <c r="W8" s="79"/>
+      <c r="X8" s="54">
         <v>1</v>
       </c>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="49" t="s">
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="AB8" s="49"/>
-      <c r="AC8" s="62">
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="76">
         <v>1000</v>
       </c>
-      <c r="AD8" s="62"/>
-      <c r="AE8" s="62"/>
-      <c r="AF8" s="113">
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="108">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="AG8" s="114"/>
-      <c r="AH8" s="114"/>
-      <c r="AI8" s="115"/>
-      <c r="AJ8" s="116">
+      <c r="AG8" s="109"/>
+      <c r="AH8" s="109"/>
+      <c r="AI8" s="110"/>
+      <c r="AJ8" s="117">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="AK8" s="116"/>
-      <c r="AL8" s="116"/>
-      <c r="AM8" s="116"/>
+      <c r="AK8" s="117"/>
+      <c r="AL8" s="117"/>
+      <c r="AM8" s="117"/>
     </row>
     <row r="9" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
       <c r="F9" s="2">
         <v>8</v>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="54">
         <v>2</v>
       </c>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="49" t="s">
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="49"/>
-      <c r="L9" s="63">
+      <c r="K9" s="55"/>
+      <c r="L9" s="75">
         <v>1000</v>
       </c>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="113">
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="108">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P9" s="114"/>
-      <c r="Q9" s="114"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="113">
+      <c r="P9" s="109"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="110"/>
+      <c r="S9" s="59"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="61"/>
+      <c r="X9" s="55"/>
+      <c r="Y9" s="55"/>
+      <c r="Z9" s="55"/>
+      <c r="AA9" s="55"/>
+      <c r="AB9" s="55"/>
+      <c r="AC9" s="55"/>
+      <c r="AD9" s="55"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG9" s="114"/>
-      <c r="AH9" s="114"/>
-      <c r="AI9" s="115"/>
-      <c r="AJ9" s="116">
+      <c r="AG9" s="109"/>
+      <c r="AH9" s="109"/>
+      <c r="AI9" s="110"/>
+      <c r="AJ9" s="117">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="AK9" s="116"/>
-      <c r="AL9" s="116"/>
-      <c r="AM9" s="116"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
+      <c r="AM9" s="117"/>
     </row>
     <row r="10" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="113">
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P10" s="114"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="115"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="49"/>
-      <c r="Z10" s="49"/>
-      <c r="AA10" s="49"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="49"/>
-      <c r="AE10" s="49"/>
-      <c r="AF10" s="113">
+      <c r="P10" s="109"/>
+      <c r="Q10" s="109"/>
+      <c r="R10" s="110"/>
+      <c r="S10" s="59"/>
+      <c r="T10" s="60"/>
+      <c r="U10" s="60"/>
+      <c r="V10" s="60"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="55"/>
+      <c r="Y10" s="55"/>
+      <c r="Z10" s="55"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="55"/>
+      <c r="AC10" s="55"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="114"/>
-      <c r="AH10" s="114"/>
-      <c r="AI10" s="115"/>
-      <c r="AJ10" s="116">
+      <c r="AG10" s="109"/>
+      <c r="AH10" s="109"/>
+      <c r="AI10" s="110"/>
+      <c r="AJ10" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="116"/>
-      <c r="AL10" s="116"/>
-      <c r="AM10" s="116"/>
+      <c r="AK10" s="117"/>
+      <c r="AL10" s="117"/>
+      <c r="AM10" s="117"/>
     </row>
     <row r="11" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="49"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="113">
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="115"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="49"/>
-      <c r="AA11" s="49"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="49"/>
-      <c r="AE11" s="49"/>
-      <c r="AF11" s="113">
+      <c r="P11" s="109"/>
+      <c r="Q11" s="109"/>
+      <c r="R11" s="110"/>
+      <c r="S11" s="59"/>
+      <c r="T11" s="60"/>
+      <c r="U11" s="60"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="55"/>
+      <c r="AC11" s="55"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="114"/>
-      <c r="AH11" s="114"/>
-      <c r="AI11" s="115"/>
-      <c r="AJ11" s="116">
+      <c r="AG11" s="109"/>
+      <c r="AH11" s="109"/>
+      <c r="AI11" s="110"/>
+      <c r="AJ11" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="116"/>
-      <c r="AL11" s="116"/>
-      <c r="AM11" s="116"/>
+      <c r="AK11" s="117"/>
+      <c r="AL11" s="117"/>
+      <c r="AM11" s="117"/>
     </row>
     <row r="12" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="49"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="113">
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="114"/>
-      <c r="R12" s="115"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-      <c r="AA12" s="49"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="49"/>
-      <c r="AE12" s="49"/>
-      <c r="AF12" s="113">
+      <c r="P12" s="109"/>
+      <c r="Q12" s="109"/>
+      <c r="R12" s="110"/>
+      <c r="S12" s="59"/>
+      <c r="T12" s="60"/>
+      <c r="U12" s="60"/>
+      <c r="V12" s="60"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="55"/>
+      <c r="AC12" s="55"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="114"/>
-      <c r="AH12" s="114"/>
-      <c r="AI12" s="115"/>
-      <c r="AJ12" s="116">
+      <c r="AG12" s="109"/>
+      <c r="AH12" s="109"/>
+      <c r="AI12" s="110"/>
+      <c r="AJ12" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="116"/>
-      <c r="AL12" s="116"/>
-      <c r="AM12" s="116"/>
+      <c r="AK12" s="117"/>
+      <c r="AL12" s="117"/>
+      <c r="AM12" s="117"/>
     </row>
     <row r="13" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="113">
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="114"/>
-      <c r="R13" s="115"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="49"/>
-      <c r="AA13" s="49"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="49"/>
-      <c r="AF13" s="113">
+      <c r="P13" s="109"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="110"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="60"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="61"/>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="55"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="55"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="114"/>
-      <c r="AH13" s="114"/>
-      <c r="AI13" s="115"/>
-      <c r="AJ13" s="116">
+      <c r="AG13" s="109"/>
+      <c r="AH13" s="109"/>
+      <c r="AI13" s="110"/>
+      <c r="AJ13" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="116"/>
-      <c r="AL13" s="116"/>
-      <c r="AM13" s="116"/>
+      <c r="AK13" s="117"/>
+      <c r="AL13" s="117"/>
+      <c r="AM13" s="117"/>
     </row>
     <row r="14" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="49"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
+      <c r="A14" s="55"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
-      <c r="O14" s="113">
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="115"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="49"/>
-      <c r="Y14" s="49"/>
-      <c r="Z14" s="49"/>
-      <c r="AA14" s="49"/>
-      <c r="AB14" s="49"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="49"/>
-      <c r="AF14" s="113">
+      <c r="P14" s="109"/>
+      <c r="Q14" s="109"/>
+      <c r="R14" s="110"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="60"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="55"/>
+      <c r="Y14" s="55"/>
+      <c r="Z14" s="55"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="55"/>
+      <c r="AC14" s="55"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="55"/>
+      <c r="AF14" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="114"/>
-      <c r="AH14" s="114"/>
-      <c r="AI14" s="115"/>
-      <c r="AJ14" s="116">
+      <c r="AG14" s="109"/>
+      <c r="AH14" s="109"/>
+      <c r="AI14" s="110"/>
+      <c r="AJ14" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="116"/>
-      <c r="AL14" s="116"/>
-      <c r="AM14" s="116"/>
+      <c r="AK14" s="117"/>
+      <c r="AL14" s="117"/>
+      <c r="AM14" s="117"/>
     </row>
     <row r="15" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="49"/>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="113">
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="115"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-      <c r="W15" s="57"/>
-      <c r="X15" s="49"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="49"/>
-      <c r="AA15" s="49"/>
-      <c r="AB15" s="49"/>
-      <c r="AC15" s="49"/>
-      <c r="AD15" s="49"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="113">
+      <c r="P15" s="109"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="59"/>
+      <c r="T15" s="60"/>
+      <c r="U15" s="60"/>
+      <c r="V15" s="60"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="55"/>
+      <c r="Y15" s="55"/>
+      <c r="Z15" s="55"/>
+      <c r="AA15" s="55"/>
+      <c r="AB15" s="55"/>
+      <c r="AC15" s="55"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="55"/>
+      <c r="AF15" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="115"/>
-      <c r="AJ15" s="116">
+      <c r="AG15" s="109"/>
+      <c r="AH15" s="109"/>
+      <c r="AI15" s="110"/>
+      <c r="AJ15" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="116"/>
-      <c r="AL15" s="116"/>
-      <c r="AM15" s="116"/>
+      <c r="AK15" s="117"/>
+      <c r="AL15" s="117"/>
+      <c r="AM15" s="117"/>
     </row>
     <row r="16" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="49"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="113">
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="115"/>
-      <c r="S16" s="55"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
-      <c r="V16" s="56"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="49"/>
-      <c r="AA16" s="49"/>
-      <c r="AB16" s="49"/>
-      <c r="AC16" s="49"/>
-      <c r="AD16" s="49"/>
-      <c r="AE16" s="49"/>
-      <c r="AF16" s="113">
+      <c r="P16" s="109"/>
+      <c r="Q16" s="109"/>
+      <c r="R16" s="110"/>
+      <c r="S16" s="59"/>
+      <c r="T16" s="60"/>
+      <c r="U16" s="60"/>
+      <c r="V16" s="60"/>
+      <c r="W16" s="61"/>
+      <c r="X16" s="55"/>
+      <c r="Y16" s="55"/>
+      <c r="Z16" s="55"/>
+      <c r="AA16" s="55"/>
+      <c r="AB16" s="55"/>
+      <c r="AC16" s="55"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="55"/>
+      <c r="AF16" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="114"/>
-      <c r="AH16" s="114"/>
-      <c r="AI16" s="115"/>
-      <c r="AJ16" s="116">
+      <c r="AG16" s="109"/>
+      <c r="AH16" s="109"/>
+      <c r="AI16" s="110"/>
+      <c r="AJ16" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="116"/>
-      <c r="AL16" s="116"/>
-      <c r="AM16" s="116"/>
+      <c r="AK16" s="117"/>
+      <c r="AL16" s="117"/>
+      <c r="AM16" s="117"/>
     </row>
     <row r="17" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
+      <c r="A17" s="55"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="113">
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
-      <c r="V17" s="56"/>
-      <c r="W17" s="57"/>
-      <c r="X17" s="49"/>
-      <c r="Y17" s="49"/>
-      <c r="Z17" s="49"/>
-      <c r="AA17" s="49"/>
-      <c r="AB17" s="49"/>
-      <c r="AC17" s="49"/>
-      <c r="AD17" s="49"/>
-      <c r="AE17" s="49"/>
-      <c r="AF17" s="113">
+      <c r="P17" s="109"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="110"/>
+      <c r="S17" s="59"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="61"/>
+      <c r="X17" s="55"/>
+      <c r="Y17" s="55"/>
+      <c r="Z17" s="55"/>
+      <c r="AA17" s="55"/>
+      <c r="AB17" s="55"/>
+      <c r="AC17" s="55"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="55"/>
+      <c r="AF17" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="114"/>
-      <c r="AH17" s="114"/>
-      <c r="AI17" s="115"/>
-      <c r="AJ17" s="116">
+      <c r="AG17" s="109"/>
+      <c r="AH17" s="109"/>
+      <c r="AI17" s="110"/>
+      <c r="AJ17" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="116"/>
-      <c r="AL17" s="116"/>
-      <c r="AM17" s="116"/>
+      <c r="AK17" s="117"/>
+      <c r="AL17" s="117"/>
+      <c r="AM17" s="117"/>
     </row>
     <row r="18" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="54"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="113">
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="114"/>
-      <c r="Q18" s="114"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
-      <c r="V18" s="56"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
-      <c r="Z18" s="49"/>
-      <c r="AA18" s="49"/>
-      <c r="AB18" s="49"/>
-      <c r="AC18" s="49"/>
-      <c r="AD18" s="49"/>
-      <c r="AE18" s="49"/>
-      <c r="AF18" s="113">
+      <c r="P18" s="109"/>
+      <c r="Q18" s="109"/>
+      <c r="R18" s="110"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="60"/>
+      <c r="U18" s="60"/>
+      <c r="V18" s="60"/>
+      <c r="W18" s="61"/>
+      <c r="X18" s="55"/>
+      <c r="Y18" s="55"/>
+      <c r="Z18" s="55"/>
+      <c r="AA18" s="55"/>
+      <c r="AB18" s="55"/>
+      <c r="AC18" s="55"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="55"/>
+      <c r="AF18" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="114"/>
-      <c r="AH18" s="114"/>
-      <c r="AI18" s="115"/>
-      <c r="AJ18" s="116">
+      <c r="AG18" s="109"/>
+      <c r="AH18" s="109"/>
+      <c r="AI18" s="110"/>
+      <c r="AJ18" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="116"/>
-      <c r="AL18" s="116"/>
-      <c r="AM18" s="116"/>
+      <c r="AK18" s="117"/>
+      <c r="AL18" s="117"/>
+      <c r="AM18" s="117"/>
     </row>
     <row r="19" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
+      <c r="A19" s="55"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="54"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="113">
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="114"/>
-      <c r="Q19" s="114"/>
-      <c r="R19" s="115"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="49"/>
-      <c r="Y19" s="49"/>
-      <c r="Z19" s="49"/>
-      <c r="AA19" s="49"/>
-      <c r="AB19" s="49"/>
-      <c r="AC19" s="49"/>
-      <c r="AD19" s="49"/>
-      <c r="AE19" s="49"/>
-      <c r="AF19" s="113">
+      <c r="P19" s="109"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="59"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="55"/>
+      <c r="Y19" s="55"/>
+      <c r="Z19" s="55"/>
+      <c r="AA19" s="55"/>
+      <c r="AB19" s="55"/>
+      <c r="AC19" s="55"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="55"/>
+      <c r="AF19" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="114"/>
-      <c r="AH19" s="114"/>
-      <c r="AI19" s="115"/>
-      <c r="AJ19" s="116">
+      <c r="AG19" s="109"/>
+      <c r="AH19" s="109"/>
+      <c r="AI19" s="110"/>
+      <c r="AJ19" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="116"/>
-      <c r="AL19" s="116"/>
-      <c r="AM19" s="116"/>
+      <c r="AK19" s="117"/>
+      <c r="AL19" s="117"/>
+      <c r="AM19" s="117"/>
     </row>
     <row r="20" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="113">
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="115"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="49"/>
-      <c r="Y20" s="49"/>
-      <c r="Z20" s="49"/>
-      <c r="AA20" s="49"/>
-      <c r="AB20" s="49"/>
-      <c r="AC20" s="49"/>
-      <c r="AD20" s="49"/>
-      <c r="AE20" s="49"/>
-      <c r="AF20" s="113">
+      <c r="P20" s="109"/>
+      <c r="Q20" s="109"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="60"/>
+      <c r="U20" s="60"/>
+      <c r="V20" s="60"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="55"/>
+      <c r="Y20" s="55"/>
+      <c r="Z20" s="55"/>
+      <c r="AA20" s="55"/>
+      <c r="AB20" s="55"/>
+      <c r="AC20" s="55"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="55"/>
+      <c r="AF20" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="114"/>
-      <c r="AH20" s="114"/>
-      <c r="AI20" s="115"/>
-      <c r="AJ20" s="116">
+      <c r="AG20" s="109"/>
+      <c r="AH20" s="109"/>
+      <c r="AI20" s="110"/>
+      <c r="AJ20" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="116"/>
-      <c r="AL20" s="116"/>
-      <c r="AM20" s="116"/>
+      <c r="AK20" s="117"/>
+      <c r="AL20" s="117"/>
+      <c r="AM20" s="117"/>
     </row>
     <row r="21" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="113">
+      <c r="G21" s="55"/>
+      <c r="H21" s="55"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="55"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="114"/>
-      <c r="R21" s="115"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="56"/>
-      <c r="U21" s="56"/>
-      <c r="V21" s="56"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="49"/>
-      <c r="Y21" s="49"/>
-      <c r="Z21" s="49"/>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="49"/>
-      <c r="AF21" s="113">
+      <c r="P21" s="109"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="110"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="60"/>
+      <c r="U21" s="60"/>
+      <c r="V21" s="60"/>
+      <c r="W21" s="61"/>
+      <c r="X21" s="55"/>
+      <c r="Y21" s="55"/>
+      <c r="Z21" s="55"/>
+      <c r="AA21" s="55"/>
+      <c r="AB21" s="55"/>
+      <c r="AC21" s="55"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="55"/>
+      <c r="AF21" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="114"/>
-      <c r="AH21" s="114"/>
-      <c r="AI21" s="115"/>
-      <c r="AJ21" s="116">
+      <c r="AG21" s="109"/>
+      <c r="AH21" s="109"/>
+      <c r="AI21" s="110"/>
+      <c r="AJ21" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="116"/>
-      <c r="AL21" s="116"/>
-      <c r="AM21" s="116"/>
+      <c r="AK21" s="117"/>
+      <c r="AL21" s="117"/>
+      <c r="AM21" s="117"/>
     </row>
     <row r="22" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
+      <c r="A22" s="55"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="113">
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="108">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="115"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="56"/>
-      <c r="U22" s="56"/>
-      <c r="V22" s="56"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="49"/>
-      <c r="Y22" s="49"/>
-      <c r="Z22" s="49"/>
-      <c r="AA22" s="49"/>
-      <c r="AB22" s="49"/>
-      <c r="AC22" s="49"/>
-      <c r="AD22" s="49"/>
-      <c r="AE22" s="49"/>
-      <c r="AF22" s="113">
+      <c r="P22" s="109"/>
+      <c r="Q22" s="109"/>
+      <c r="R22" s="110"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="60"/>
+      <c r="U22" s="60"/>
+      <c r="V22" s="60"/>
+      <c r="W22" s="61"/>
+      <c r="X22" s="55"/>
+      <c r="Y22" s="55"/>
+      <c r="Z22" s="55"/>
+      <c r="AA22" s="55"/>
+      <c r="AB22" s="55"/>
+      <c r="AC22" s="55"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="55"/>
+      <c r="AF22" s="108">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="114"/>
-      <c r="AH22" s="114"/>
-      <c r="AI22" s="115"/>
-      <c r="AJ22" s="116">
+      <c r="AG22" s="109"/>
+      <c r="AH22" s="109"/>
+      <c r="AI22" s="110"/>
+      <c r="AJ22" s="117">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="116"/>
-      <c r="AL22" s="116"/>
-      <c r="AM22" s="116"/>
+      <c r="AK22" s="117"/>
+      <c r="AL22" s="117"/>
+      <c r="AM22" s="117"/>
     </row>
     <row r="23" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="53">
+      <c r="G23" s="54">
         <f>SUM(G6:G22)</f>
         <v>8</v>
       </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="110">
+      <c r="H23" s="54"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="119">
         <f>SUM(O6:O22)</f>
         <v>8000</v>
       </c>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
-      <c r="Z23" s="49"/>
-      <c r="AA23" s="49"/>
-      <c r="AB23" s="49"/>
-      <c r="AC23" s="49"/>
-      <c r="AD23" s="49"/>
-      <c r="AE23" s="49"/>
-      <c r="AF23" s="110">
+      <c r="P23" s="120"/>
+      <c r="Q23" s="120"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="60"/>
+      <c r="U23" s="60"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="55"/>
+      <c r="Y23" s="55"/>
+      <c r="Z23" s="55"/>
+      <c r="AA23" s="55"/>
+      <c r="AB23" s="55"/>
+      <c r="AC23" s="55"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="55"/>
+      <c r="AF23" s="119">
         <f>SUM(AF6:AF22)</f>
         <v>2800</v>
       </c>
-      <c r="AG23" s="111"/>
-      <c r="AH23" s="111"/>
-      <c r="AI23" s="112"/>
-      <c r="AJ23" s="110">
+      <c r="AG23" s="120"/>
+      <c r="AH23" s="120"/>
+      <c r="AI23" s="121"/>
+      <c r="AJ23" s="119">
         <f>SUM(AJ6:AJ22)</f>
         <v>10800</v>
       </c>
-      <c r="AK23" s="111"/>
-      <c r="AL23" s="111"/>
-      <c r="AM23" s="112"/>
+      <c r="AK23" s="120"/>
+      <c r="AL23" s="120"/>
+      <c r="AM23" s="121"/>
     </row>
     <row r="24" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9" t="s">
@@ -6441,28 +6439,176 @@
     </row>
   </sheetData>
   <mergeCells count="216">
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="S6:W6"/>
-    <mergeCell ref="X6:Z6"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:AD3"/>
-    <mergeCell ref="AE3:AI3"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="G4:R4"/>
-    <mergeCell ref="S4:AI4"/>
-    <mergeCell ref="AJ4:AM5"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="AF5:AI5"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="S5:W5"/>
-    <mergeCell ref="X5:AB5"/>
-    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="X23:Z23"/>
+    <mergeCell ref="AA23:AB23"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S23:W23"/>
+    <mergeCell ref="S22:W22"/>
+    <mergeCell ref="X22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="AJ22:AM22"/>
+    <mergeCell ref="X21:Z21"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="AJ21:AM21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:R22"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="S20:W20"/>
+    <mergeCell ref="X20:Z20"/>
+    <mergeCell ref="AA20:AB20"/>
+    <mergeCell ref="AC20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="AJ20:AM20"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AB19"/>
+    <mergeCell ref="AC19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="AJ19:AM19"/>
+    <mergeCell ref="S19:W19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:R20"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:R19"/>
+    <mergeCell ref="S18:W18"/>
+    <mergeCell ref="X18:Z18"/>
+    <mergeCell ref="AA18:AB18"/>
+    <mergeCell ref="AC18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="AJ18:AM18"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="AA17:AB17"/>
+    <mergeCell ref="AC17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="AJ17:AM17"/>
+    <mergeCell ref="S17:W17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:R18"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="S16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AA16:AB16"/>
+    <mergeCell ref="AC16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="AJ16:AM16"/>
+    <mergeCell ref="X15:Z15"/>
+    <mergeCell ref="AA15:AB15"/>
+    <mergeCell ref="AC15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="AJ15:AM15"/>
+    <mergeCell ref="S15:W15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="S14:W14"/>
+    <mergeCell ref="X14:Z14"/>
+    <mergeCell ref="AA14:AB14"/>
+    <mergeCell ref="AC14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="AJ14:AM14"/>
+    <mergeCell ref="X13:Z13"/>
+    <mergeCell ref="AA13:AB13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="AJ13:AM13"/>
+    <mergeCell ref="S13:W13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="S12:W12"/>
+    <mergeCell ref="X12:Z12"/>
+    <mergeCell ref="AA12:AB12"/>
+    <mergeCell ref="AC12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="AJ12:AM12"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AB11"/>
+    <mergeCell ref="AC11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="AJ11:AM11"/>
+    <mergeCell ref="S11:W11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="AA10:AB10"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="X9:Z9"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="AC9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="AJ9:AM9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AC8:AE8"/>
+    <mergeCell ref="AF8:AI8"/>
+    <mergeCell ref="AJ8:AM8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="S8:W8"/>
+    <mergeCell ref="X8:Z8"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="J10:K10"/>
@@ -6487,176 +6633,28 @@
     <mergeCell ref="G6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="L6:N6"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AF8:AI8"/>
-    <mergeCell ref="AJ8:AM8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="S8:W8"/>
-    <mergeCell ref="X8:Z8"/>
-    <mergeCell ref="AA10:AB10"/>
-    <mergeCell ref="AC10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="X9:Z9"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="AC9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="AJ9:AM9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="S12:W12"/>
-    <mergeCell ref="X12:Z12"/>
-    <mergeCell ref="AA12:AB12"/>
-    <mergeCell ref="AC12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="AJ12:AM12"/>
-    <mergeCell ref="X11:Z11"/>
-    <mergeCell ref="AA11:AB11"/>
-    <mergeCell ref="AC11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="AJ11:AM11"/>
-    <mergeCell ref="S11:W11"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="S14:W14"/>
-    <mergeCell ref="X14:Z14"/>
-    <mergeCell ref="AA14:AB14"/>
-    <mergeCell ref="AC14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="AJ14:AM14"/>
-    <mergeCell ref="X13:Z13"/>
-    <mergeCell ref="AA13:AB13"/>
-    <mergeCell ref="AC13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="AJ13:AM13"/>
-    <mergeCell ref="S13:W13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="S16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AA16:AB16"/>
-    <mergeCell ref="AC16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="AJ16:AM16"/>
-    <mergeCell ref="X15:Z15"/>
-    <mergeCell ref="AA15:AB15"/>
-    <mergeCell ref="AC15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="AJ15:AM15"/>
-    <mergeCell ref="S15:W15"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:R18"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="S18:W18"/>
-    <mergeCell ref="X18:Z18"/>
-    <mergeCell ref="AA18:AB18"/>
-    <mergeCell ref="AC18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="AJ18:AM18"/>
-    <mergeCell ref="X17:Z17"/>
-    <mergeCell ref="AA17:AB17"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="AJ17:AM17"/>
-    <mergeCell ref="S17:W17"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:R20"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:R19"/>
-    <mergeCell ref="S21:W21"/>
-    <mergeCell ref="S20:W20"/>
-    <mergeCell ref="X20:Z20"/>
-    <mergeCell ref="AA20:AB20"/>
-    <mergeCell ref="AC20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="AJ20:AM20"/>
-    <mergeCell ref="X19:Z19"/>
-    <mergeCell ref="AA19:AB19"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="AJ19:AM19"/>
-    <mergeCell ref="S19:W19"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="O22:R22"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="X23:Z23"/>
-    <mergeCell ref="AA23:AB23"/>
-    <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="AJ23:AM23"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S23:W23"/>
-    <mergeCell ref="S22:W22"/>
-    <mergeCell ref="X22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="AJ22:AM22"/>
-    <mergeCell ref="X21:Z21"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="AC21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="AJ21:AM21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:W6"/>
+    <mergeCell ref="X6:Z6"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:AD3"/>
+    <mergeCell ref="AE3:AI3"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="G4:R4"/>
+    <mergeCell ref="S4:AI4"/>
+    <mergeCell ref="AJ4:AM5"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="AF5:AI5"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="S5:W5"/>
+    <mergeCell ref="X5:AB5"/>
+    <mergeCell ref="AC5:AE5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>

--- a/frontend/public/様式1_活動報告書_農地維持支払.xlsx
+++ b/frontend/public/様式1_活動報告書_農地維持支払.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taros\Documents\Koyu\dev\tamokuteki_kinouhakki_sokushin_erp\frontend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB906268-FF81-4AF0-BA12-EFEA564D8EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F8493F-16DF-44BA-91BB-B47A1BFDB6C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9960" yWindow="3288" windowWidth="34560" windowHeight="18600" activeTab="1" xr2:uid="{F21A66FA-6EBE-4524-A7C7-D4EDBA8E7EA2}"/>
+    <workbookView xWindow="25596" yWindow="3192" windowWidth="20184" windowHeight="18600" xr2:uid="{F21A66FA-6EBE-4524-A7C7-D4EDBA8E7EA2}"/>
   </bookViews>
   <sheets>
     <sheet name="活動報告書" sheetId="8" r:id="rId1"/>
@@ -1201,7 +1201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1274,6 +1274,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1331,9 +1409,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1346,21 +1421,9 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1384,72 +1447,6 @@
     </xf>
     <xf numFmtId="38" fontId="0" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1899,335 +1896,333 @@
       </c>
     </row>
     <row r="2" spans="1:37" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="67"/>
-      <c r="AH2" s="67"/>
-      <c r="AI2" s="67"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
+      <c r="AE2" s="30"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="30"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="30"/>
     </row>
     <row r="3" spans="1:37" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="O3" s="43" t="s">
+      <c r="O3" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43">
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24">
         <v>130</v>
       </c>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43" t="s">
+      <c r="S3" s="24"/>
+      <c r="T3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43" t="s">
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
       <c r="AK3" s="21"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43" t="s">
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="61" t="s">
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="43" t="s">
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="43"/>
-      <c r="AD4" s="43"/>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="43"/>
-      <c r="AG4" s="43"/>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="43"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
     </row>
     <row r="5" spans="1:37" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43" t="s">
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="43"/>
-      <c r="O5" s="48" t="s">
+      <c r="N5" s="24"/>
+      <c r="O5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48" t="s">
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="48"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="63"/>
-      <c r="Z5" s="64"/>
-      <c r="AA5" s="43"/>
-      <c r="AB5" s="43"/>
-      <c r="AC5" s="43"/>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="43"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="43"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
     </row>
     <row r="6" spans="1:37" s="21" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43" t="s">
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="66"/>
-      <c r="AA6" s="43"/>
-      <c r="AB6" s="43"/>
-      <c r="AC6" s="43"/>
-      <c r="AD6" s="43"/>
-      <c r="AE6" s="43"/>
-      <c r="AF6" s="43"/>
-      <c r="AG6" s="43"/>
-      <c r="AH6" s="43"/>
-      <c r="AI6" s="43"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
     </row>
     <row r="7" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="76"/>
-      <c r="B7" s="76"/>
-      <c r="C7" s="77" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="80" t="s">
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43" t="s">
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="52"/>
-      <c r="Y7" s="43">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="43"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="43"/>
-      <c r="AD7" s="43"/>
-      <c r="AE7" s="43"/>
-      <c r="AF7" s="43"/>
-      <c r="AG7" s="43"/>
-      <c r="AH7" s="43"/>
-      <c r="AI7" s="43"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="46"/>
+      <c r="T7" s="47"/>
+      <c r="U7" s="47"/>
+      <c r="V7" s="47"/>
+      <c r="W7" s="47"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
     </row>
     <row r="8" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="69"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="69"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69"/>
-      <c r="AF8" s="69"/>
-      <c r="AG8" s="69"/>
-      <c r="AH8" s="69"/>
-      <c r="AI8" s="70"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="33"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="33"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="35"/>
     </row>
     <row r="9" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="71"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="72"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="72"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="72"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
-      <c r="AC9" s="72"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="72"/>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="73"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="38"/>
     </row>
     <row r="10" spans="1:37" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="Y10" s="10" t="s">
@@ -2235,26 +2230,26 @@
       </c>
     </row>
     <row r="11" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="48" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="L11" s="43"/>
-      <c r="M11" s="74" t="s">
+      <c r="L11" s="24"/>
+      <c r="M11" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="N11" s="75"/>
+      <c r="N11" s="40"/>
       <c r="Y11" s="10" t="s">
         <v>28</v>
       </c>
@@ -2263,21 +2258,21 @@
       <c r="A12" s="19">
         <v>1</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="81"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
       <c r="Y12" s="10" t="s">
         <v>29</v>
       </c>
@@ -2286,23 +2281,23 @@
       <c r="A13" s="19">
         <v>2</v>
       </c>
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="82" t="s">
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
       <c r="Y13" s="10" t="s">
         <v>30</v>
       </c>
@@ -2311,41 +2306,41 @@
       <c r="A14" s="19">
         <v>3</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
     </row>
     <row r="15" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="19">
         <v>4</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="81"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
       <c r="W15" s="22" t="s">
         <v>57</v>
       </c>
@@ -2354,50 +2349,50 @@
       <c r="A16" s="19">
         <v>5</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="81"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="43"/>
-      <c r="AH16" s="43"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="24"/>
     </row>
     <row r="17" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="W17" s="43"/>
-      <c r="X17" s="43"/>
-      <c r="Y17" s="43"/>
-      <c r="Z17" s="43"/>
-      <c r="AA17" s="43"/>
-      <c r="AB17" s="43"/>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="43"/>
-      <c r="AE17" s="43"/>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="43"/>
-      <c r="AH17" s="43"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
+      <c r="AH17" s="24"/>
     </row>
     <row r="18" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -2423,7 +2418,6 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="M16:N16"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="AA7:AI7"/>
     <mergeCell ref="A8:AI9"/>
     <mergeCell ref="A11:J11"/>
@@ -2437,6 +2431,7 @@
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="S7:X7"/>
+    <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="A2:AI2"/>
     <mergeCell ref="T3:V3"/>
     <mergeCell ref="W3:AD3"/>
@@ -2488,3095 +2483,3095 @@
       </c>
     </row>
     <row r="2" spans="1:39" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="64"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="64"/>
+      <c r="AG2" s="64"/>
+      <c r="AH2" s="64"/>
+      <c r="AI2" s="64"/>
+      <c r="AJ2" s="64"/>
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="64"/>
+      <c r="AM2" s="64"/>
     </row>
     <row r="3" spans="1:39" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="Q3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="39" t="str">
+      <c r="Q3" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="65" t="str">
         <f>IF(活動報告書!W3="","",活動報告書!W3)</f>
         <v>鎌田緑保護会</v>
       </c>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="30" t="s">
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="40" t="str">
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="66" t="str">
         <f>IF(活動報告書!A7="","",活動報告書!A7)</f>
         <v/>
       </c>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="67"/>
+      <c r="AM3" s="67"/>
     </row>
     <row r="4" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="28" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="30" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
-      <c r="AH4" s="31"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="42" t="s">
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="57"/>
+      <c r="AC4" s="57"/>
+      <c r="AD4" s="57"/>
+      <c r="AE4" s="57"/>
+      <c r="AF4" s="57"/>
+      <c r="AG4" s="57"/>
+      <c r="AH4" s="57"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="42"/>
-      <c r="AL4" s="42"/>
-      <c r="AM4" s="42"/>
+      <c r="AK4" s="68"/>
+      <c r="AL4" s="68"/>
+      <c r="AM4" s="68"/>
     </row>
     <row r="5" spans="1:39" s="10" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="44" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="50" t="s">
+      <c r="P5" s="70"/>
+      <c r="Q5" s="70"/>
+      <c r="R5" s="73"/>
+      <c r="S5" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="48" t="s">
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48" t="s">
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="44" t="s">
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="46"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="42"/>
-      <c r="AK5" s="42"/>
-      <c r="AL5" s="42"/>
-      <c r="AM5" s="42"/>
+      <c r="AG5" s="70"/>
+      <c r="AH5" s="71"/>
+      <c r="AI5" s="72"/>
+      <c r="AJ5" s="68"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
     </row>
     <row r="6" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="24">
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="50">
         <f t="shared" ref="O6:O62" si="0">G6*L6</f>
         <v>0</v>
       </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="26"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="24">
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="60"/>
+      <c r="U6" s="60"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="62"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="54"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="50">
         <f t="shared" ref="AF6:AF62" si="1">X6*AC6</f>
         <v>0</v>
       </c>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="26"/>
-      <c r="AJ6" s="27">
+      <c r="AG6" s="51"/>
+      <c r="AH6" s="51"/>
+      <c r="AI6" s="52"/>
+      <c r="AJ6" s="53">
         <f>O6+AF6</f>
         <v>0</v>
       </c>
-      <c r="AK6" s="27"/>
-      <c r="AL6" s="27"/>
-      <c r="AM6" s="27"/>
+      <c r="AK6" s="53"/>
+      <c r="AL6" s="53"/>
+      <c r="AM6" s="53"/>
     </row>
     <row r="7" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="24">
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="35"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="24">
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="59"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="61"/>
+      <c r="X7" s="62"/>
+      <c r="Y7" s="62"/>
+      <c r="Z7" s="62"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63"/>
+      <c r="AF7" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="25"/>
-      <c r="AH7" s="25"/>
-      <c r="AI7" s="26"/>
-      <c r="AJ7" s="27">
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="51"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="53">
         <f t="shared" ref="AJ7:AJ62" si="2">O7+AF7</f>
         <v>0</v>
       </c>
-      <c r="AK7" s="27"/>
-      <c r="AL7" s="27"/>
-      <c r="AM7" s="27"/>
+      <c r="AK7" s="53"/>
+      <c r="AL7" s="53"/>
+      <c r="AM7" s="53"/>
     </row>
     <row r="8" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="24">
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="28"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="54"/>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="54"/>
-      <c r="AF8" s="24">
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="52"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="77"/>
+      <c r="U8" s="77"/>
+      <c r="V8" s="77"/>
+      <c r="W8" s="78"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="75"/>
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="75"/>
+      <c r="AF8" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG8" s="25"/>
-      <c r="AH8" s="25"/>
-      <c r="AI8" s="26"/>
-      <c r="AJ8" s="27">
+      <c r="AG8" s="51"/>
+      <c r="AH8" s="51"/>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK8" s="27"/>
-      <c r="AL8" s="27"/>
-      <c r="AM8" s="27"/>
+      <c r="AK8" s="53"/>
+      <c r="AL8" s="53"/>
+      <c r="AM8" s="53"/>
     </row>
     <row r="9" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="24">
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="24">
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG9" s="25"/>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="27">
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
+      <c r="AK9" s="53"/>
+      <c r="AL9" s="53"/>
+      <c r="AM9" s="53"/>
     </row>
     <row r="10" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="24">
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="28"/>
-      <c r="AE10" s="28"/>
-      <c r="AF10" s="24">
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="57"/>
+      <c r="W10" s="58"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="26"/>
-      <c r="AJ10" s="27">
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="51"/>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="27"/>
-      <c r="AL10" s="27"/>
-      <c r="AM10" s="27"/>
+      <c r="AK10" s="53"/>
+      <c r="AL10" s="53"/>
+      <c r="AM10" s="53"/>
     </row>
     <row r="11" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="24">
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="28"/>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="24">
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="26"/>
-      <c r="AJ11" s="27">
+      <c r="AG11" s="51"/>
+      <c r="AH11" s="51"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="27"/>
+      <c r="AK11" s="53"/>
+      <c r="AL11" s="53"/>
+      <c r="AM11" s="53"/>
     </row>
     <row r="12" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="24">
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="32"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="28"/>
-      <c r="AE12" s="28"/>
-      <c r="AF12" s="24">
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="25"/>
-      <c r="AI12" s="26"/>
-      <c r="AJ12" s="27">
+      <c r="AG12" s="51"/>
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="52"/>
+      <c r="AJ12" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="27"/>
-      <c r="AL12" s="27"/>
-      <c r="AM12" s="27"/>
+      <c r="AK12" s="53"/>
+      <c r="AL12" s="53"/>
+      <c r="AM12" s="53"/>
     </row>
     <row r="13" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="24">
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="24">
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="25"/>
-      <c r="AH13" s="25"/>
-      <c r="AI13" s="26"/>
-      <c r="AJ13" s="27">
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="27"/>
+      <c r="AK13" s="53"/>
+      <c r="AL13" s="53"/>
+      <c r="AM13" s="53"/>
     </row>
     <row r="14" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="24">
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="26"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="28"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="28"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="24">
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="54"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="54"/>
+      <c r="AF14" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="25"/>
-      <c r="AH14" s="25"/>
-      <c r="AI14" s="26"/>
-      <c r="AJ14" s="27">
+      <c r="AG14" s="51"/>
+      <c r="AH14" s="51"/>
+      <c r="AI14" s="52"/>
+      <c r="AJ14" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="27"/>
-      <c r="AL14" s="27"/>
-      <c r="AM14" s="27"/>
+      <c r="AK14" s="53"/>
+      <c r="AL14" s="53"/>
+      <c r="AM14" s="53"/>
     </row>
     <row r="15" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="24">
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="26"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="24">
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="58"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="54"/>
+      <c r="AF15" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="26"/>
-      <c r="AJ15" s="27">
+      <c r="AG15" s="51"/>
+      <c r="AH15" s="51"/>
+      <c r="AI15" s="52"/>
+      <c r="AJ15" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="27"/>
-      <c r="AL15" s="27"/>
-      <c r="AM15" s="27"/>
+      <c r="AK15" s="53"/>
+      <c r="AL15" s="53"/>
+      <c r="AM15" s="53"/>
     </row>
     <row r="16" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="24">
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="26"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="24">
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="52"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="58"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="54"/>
+      <c r="AF16" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="25"/>
-      <c r="AH16" s="25"/>
-      <c r="AI16" s="26"/>
-      <c r="AJ16" s="27">
+      <c r="AG16" s="51"/>
+      <c r="AH16" s="51"/>
+      <c r="AI16" s="52"/>
+      <c r="AJ16" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="27"/>
-      <c r="AL16" s="27"/>
-      <c r="AM16" s="27"/>
+      <c r="AK16" s="53"/>
+      <c r="AL16" s="53"/>
+      <c r="AM16" s="53"/>
     </row>
     <row r="17" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="24">
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="26"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="28"/>
-      <c r="AE17" s="28"/>
-      <c r="AF17" s="24">
+      <c r="P17" s="51"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="52"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="25"/>
-      <c r="AH17" s="25"/>
-      <c r="AI17" s="26"/>
-      <c r="AJ17" s="27">
+      <c r="AG17" s="51"/>
+      <c r="AH17" s="51"/>
+      <c r="AI17" s="52"/>
+      <c r="AJ17" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="27"/>
-      <c r="AL17" s="27"/>
-      <c r="AM17" s="27"/>
+      <c r="AK17" s="53"/>
+      <c r="AL17" s="53"/>
+      <c r="AM17" s="53"/>
     </row>
     <row r="18" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="24">
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="28"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="24">
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="52"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="57"/>
+      <c r="W18" s="58"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54"/>
+      <c r="AF18" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="25"/>
-      <c r="AH18" s="25"/>
-      <c r="AI18" s="26"/>
-      <c r="AJ18" s="27">
+      <c r="AG18" s="51"/>
+      <c r="AH18" s="51"/>
+      <c r="AI18" s="52"/>
+      <c r="AJ18" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="27"/>
-      <c r="AL18" s="27"/>
-      <c r="AM18" s="27"/>
+      <c r="AK18" s="53"/>
+      <c r="AL18" s="53"/>
+      <c r="AM18" s="53"/>
     </row>
     <row r="19" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="24">
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="24">
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="52"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="25"/>
-      <c r="AH19" s="25"/>
-      <c r="AI19" s="26"/>
-      <c r="AJ19" s="27">
+      <c r="AG19" s="51"/>
+      <c r="AH19" s="51"/>
+      <c r="AI19" s="52"/>
+      <c r="AJ19" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="27"/>
-      <c r="AL19" s="27"/>
-      <c r="AM19" s="27"/>
+      <c r="AK19" s="53"/>
+      <c r="AL19" s="53"/>
+      <c r="AM19" s="53"/>
     </row>
     <row r="20" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="24">
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="28"/>
-      <c r="AF20" s="24">
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="52"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="54"/>
+      <c r="AB20" s="54"/>
+      <c r="AC20" s="54"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="54"/>
+      <c r="AF20" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="25"/>
-      <c r="AH20" s="25"/>
-      <c r="AI20" s="26"/>
-      <c r="AJ20" s="27">
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="51"/>
+      <c r="AI20" s="52"/>
+      <c r="AJ20" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="27"/>
-      <c r="AL20" s="27"/>
-      <c r="AM20" s="27"/>
+      <c r="AK20" s="53"/>
+      <c r="AL20" s="53"/>
+      <c r="AM20" s="53"/>
     </row>
     <row r="21" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="24">
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="28"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="28"/>
-      <c r="AA21" s="28"/>
-      <c r="AB21" s="28"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="28"/>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="24">
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="52"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="54"/>
+      <c r="AB21" s="54"/>
+      <c r="AC21" s="54"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="54"/>
+      <c r="AF21" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="26"/>
-      <c r="AJ21" s="27">
+      <c r="AG21" s="51"/>
+      <c r="AH21" s="51"/>
+      <c r="AI21" s="52"/>
+      <c r="AJ21" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="27"/>
-      <c r="AL21" s="27"/>
-      <c r="AM21" s="27"/>
+      <c r="AK21" s="53"/>
+      <c r="AL21" s="53"/>
+      <c r="AM21" s="53"/>
     </row>
     <row r="22" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="24">
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="50">
         <f t="shared" ref="O22:O61" si="3">G22*L22</f>
         <v>0</v>
       </c>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="24">
+      <c r="P22" s="51"/>
+      <c r="Q22" s="51"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="54"/>
+      <c r="AB22" s="54"/>
+      <c r="AC22" s="54"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="54"/>
+      <c r="AF22" s="50">
         <f t="shared" ref="AF22:AF61" si="4">X22*AC22</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="25"/>
-      <c r="AH22" s="25"/>
-      <c r="AI22" s="26"/>
-      <c r="AJ22" s="27">
+      <c r="AG22" s="51"/>
+      <c r="AH22" s="51"/>
+      <c r="AI22" s="52"/>
+      <c r="AJ22" s="53">
         <f t="shared" ref="AJ22:AJ61" si="5">O22+AF22</f>
         <v>0</v>
       </c>
-      <c r="AK22" s="27"/>
-      <c r="AL22" s="27"/>
-      <c r="AM22" s="27"/>
+      <c r="AK22" s="53"/>
+      <c r="AL22" s="53"/>
+      <c r="AM22" s="53"/>
     </row>
     <row r="23" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="24">
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="24">
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG23" s="25"/>
-      <c r="AH23" s="25"/>
-      <c r="AI23" s="26"/>
-      <c r="AJ23" s="27">
+      <c r="AG23" s="51"/>
+      <c r="AH23" s="51"/>
+      <c r="AI23" s="52"/>
+      <c r="AJ23" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK23" s="27"/>
-      <c r="AL23" s="27"/>
-      <c r="AM23" s="27"/>
+      <c r="AK23" s="53"/>
+      <c r="AL23" s="53"/>
+      <c r="AM23" s="53"/>
     </row>
     <row r="24" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="24">
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="55"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="28"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="28"/>
-      <c r="AB24" s="28"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="28"/>
-      <c r="AE24" s="28"/>
-      <c r="AF24" s="24">
+      <c r="P24" s="51"/>
+      <c r="Q24" s="51"/>
+      <c r="R24" s="52"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="57"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="54"/>
+      <c r="Y24" s="54"/>
+      <c r="Z24" s="54"/>
+      <c r="AA24" s="54"/>
+      <c r="AB24" s="54"/>
+      <c r="AC24" s="54"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="54"/>
+      <c r="AF24" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG24" s="25"/>
-      <c r="AH24" s="25"/>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="27">
+      <c r="AG24" s="51"/>
+      <c r="AH24" s="51"/>
+      <c r="AI24" s="52"/>
+      <c r="AJ24" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK24" s="27"/>
-      <c r="AL24" s="27"/>
-      <c r="AM24" s="27"/>
+      <c r="AK24" s="53"/>
+      <c r="AL24" s="53"/>
+      <c r="AM24" s="53"/>
     </row>
     <row r="25" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="29"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29"/>
-      <c r="O25" s="24">
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="54"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="32"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="28"/>
-      <c r="AE25" s="28"/>
-      <c r="AF25" s="24">
+      <c r="P25" s="51"/>
+      <c r="Q25" s="51"/>
+      <c r="R25" s="52"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="58"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="54"/>
+      <c r="Z25" s="54"/>
+      <c r="AA25" s="54"/>
+      <c r="AB25" s="54"/>
+      <c r="AC25" s="54"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="54"/>
+      <c r="AF25" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG25" s="25"/>
-      <c r="AH25" s="25"/>
-      <c r="AI25" s="26"/>
-      <c r="AJ25" s="27">
+      <c r="AG25" s="51"/>
+      <c r="AH25" s="51"/>
+      <c r="AI25" s="52"/>
+      <c r="AJ25" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK25" s="27"/>
-      <c r="AL25" s="27"/>
-      <c r="AM25" s="27"/>
+      <c r="AK25" s="53"/>
+      <c r="AL25" s="53"/>
+      <c r="AM25" s="53"/>
     </row>
     <row r="26" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="24">
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="55"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="32"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
-      <c r="AE26" s="28"/>
-      <c r="AF26" s="24">
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="54"/>
+      <c r="Y26" s="54"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="54"/>
+      <c r="AB26" s="54"/>
+      <c r="AC26" s="54"/>
+      <c r="AD26" s="54"/>
+      <c r="AE26" s="54"/>
+      <c r="AF26" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="26"/>
-      <c r="AJ26" s="27">
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="52"/>
+      <c r="AJ26" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK26" s="27"/>
-      <c r="AL26" s="27"/>
-      <c r="AM26" s="27"/>
+      <c r="AK26" s="53"/>
+      <c r="AL26" s="53"/>
+      <c r="AM26" s="53"/>
     </row>
     <row r="27" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
+      <c r="A27" s="54"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="24">
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="31"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="31"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="28"/>
-      <c r="AF27" s="24">
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="54"/>
+      <c r="Y27" s="54"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="54"/>
+      <c r="AC27" s="54"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="27">
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK27" s="27"/>
-      <c r="AL27" s="27"/>
-      <c r="AM27" s="27"/>
+      <c r="AK27" s="53"/>
+      <c r="AL27" s="53"/>
+      <c r="AM27" s="53"/>
     </row>
     <row r="28" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="24">
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="54"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="55"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="30"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="28"/>
-      <c r="AE28" s="28"/>
-      <c r="AF28" s="24">
+      <c r="P28" s="51"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="57"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="54"/>
+      <c r="Y28" s="54"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="54"/>
+      <c r="AB28" s="54"/>
+      <c r="AC28" s="54"/>
+      <c r="AD28" s="54"/>
+      <c r="AE28" s="54"/>
+      <c r="AF28" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="26"/>
-      <c r="AJ28" s="27">
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="52"/>
+      <c r="AJ28" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK28" s="27"/>
-      <c r="AL28" s="27"/>
-      <c r="AM28" s="27"/>
+      <c r="AK28" s="53"/>
+      <c r="AL28" s="53"/>
+      <c r="AM28" s="53"/>
     </row>
     <row r="29" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
+      <c r="A29" s="54"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="24">
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="55"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="32"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="28"/>
-      <c r="AE29" s="28"/>
-      <c r="AF29" s="24">
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="58"/>
+      <c r="X29" s="54"/>
+      <c r="Y29" s="54"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="54"/>
+      <c r="AB29" s="54"/>
+      <c r="AC29" s="54"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="26"/>
-      <c r="AJ29" s="27">
+      <c r="AG29" s="51"/>
+      <c r="AH29" s="51"/>
+      <c r="AI29" s="52"/>
+      <c r="AJ29" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK29" s="27"/>
-      <c r="AL29" s="27"/>
-      <c r="AM29" s="27"/>
+      <c r="AK29" s="53"/>
+      <c r="AL29" s="53"/>
+      <c r="AM29" s="53"/>
     </row>
     <row r="30" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="24">
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="55"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="30"/>
-      <c r="T30" s="31"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="31"/>
-      <c r="W30" s="32"/>
-      <c r="X30" s="28"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="28"/>
-      <c r="AC30" s="28"/>
-      <c r="AD30" s="28"/>
-      <c r="AE30" s="28"/>
-      <c r="AF30" s="24">
+      <c r="P30" s="51"/>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="58"/>
+      <c r="X30" s="54"/>
+      <c r="Y30" s="54"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="54"/>
+      <c r="AB30" s="54"/>
+      <c r="AC30" s="54"/>
+      <c r="AD30" s="54"/>
+      <c r="AE30" s="54"/>
+      <c r="AF30" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="26"/>
-      <c r="AJ30" s="27">
+      <c r="AG30" s="51"/>
+      <c r="AH30" s="51"/>
+      <c r="AI30" s="52"/>
+      <c r="AJ30" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK30" s="27"/>
-      <c r="AL30" s="27"/>
-      <c r="AM30" s="27"/>
+      <c r="AK30" s="53"/>
+      <c r="AL30" s="53"/>
+      <c r="AM30" s="53"/>
     </row>
     <row r="31" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="24">
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="31"/>
-      <c r="V31" s="31"/>
-      <c r="W31" s="32"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
-      <c r="AD31" s="28"/>
-      <c r="AE31" s="28"/>
-      <c r="AF31" s="24">
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="58"/>
+      <c r="X31" s="54"/>
+      <c r="Y31" s="54"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="54"/>
+      <c r="AB31" s="54"/>
+      <c r="AC31" s="54"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="26"/>
-      <c r="AJ31" s="27">
+      <c r="AG31" s="51"/>
+      <c r="AH31" s="51"/>
+      <c r="AI31" s="52"/>
+      <c r="AJ31" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK31" s="27"/>
-      <c r="AL31" s="27"/>
-      <c r="AM31" s="27"/>
+      <c r="AK31" s="53"/>
+      <c r="AL31" s="53"/>
+      <c r="AM31" s="53"/>
     </row>
     <row r="32" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="24">
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="54"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="55"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
-      <c r="AE32" s="28"/>
-      <c r="AF32" s="24">
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="58"/>
+      <c r="X32" s="54"/>
+      <c r="Y32" s="54"/>
+      <c r="Z32" s="54"/>
+      <c r="AA32" s="54"/>
+      <c r="AB32" s="54"/>
+      <c r="AC32" s="54"/>
+      <c r="AD32" s="54"/>
+      <c r="AE32" s="54"/>
+      <c r="AF32" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="25"/>
-      <c r="AI32" s="26"/>
-      <c r="AJ32" s="27">
+      <c r="AG32" s="51"/>
+      <c r="AH32" s="51"/>
+      <c r="AI32" s="52"/>
+      <c r="AJ32" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK32" s="27"/>
-      <c r="AL32" s="27"/>
-      <c r="AM32" s="27"/>
+      <c r="AK32" s="53"/>
+      <c r="AL32" s="53"/>
+      <c r="AM32" s="53"/>
     </row>
     <row r="33" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="24">
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="55"/>
+      <c r="N33" s="55"/>
+      <c r="O33" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="30"/>
-      <c r="T33" s="31"/>
-      <c r="U33" s="31"/>
-      <c r="V33" s="31"/>
-      <c r="W33" s="32"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
-      <c r="AD33" s="28"/>
-      <c r="AE33" s="28"/>
-      <c r="AF33" s="24">
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="58"/>
+      <c r="X33" s="54"/>
+      <c r="Y33" s="54"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="54"/>
+      <c r="AB33" s="54"/>
+      <c r="AC33" s="54"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG33" s="25"/>
-      <c r="AH33" s="25"/>
-      <c r="AI33" s="26"/>
-      <c r="AJ33" s="27">
+      <c r="AG33" s="51"/>
+      <c r="AH33" s="51"/>
+      <c r="AI33" s="52"/>
+      <c r="AJ33" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK33" s="27"/>
-      <c r="AL33" s="27"/>
-      <c r="AM33" s="27"/>
+      <c r="AK33" s="53"/>
+      <c r="AL33" s="53"/>
+      <c r="AM33" s="53"/>
     </row>
     <row r="34" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="29"/>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="24">
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="30"/>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="32"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
-      <c r="AD34" s="28"/>
-      <c r="AE34" s="28"/>
-      <c r="AF34" s="24">
+      <c r="P34" s="51"/>
+      <c r="Q34" s="51"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="56"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="57"/>
+      <c r="V34" s="57"/>
+      <c r="W34" s="58"/>
+      <c r="X34" s="54"/>
+      <c r="Y34" s="54"/>
+      <c r="Z34" s="54"/>
+      <c r="AA34" s="54"/>
+      <c r="AB34" s="54"/>
+      <c r="AC34" s="54"/>
+      <c r="AD34" s="54"/>
+      <c r="AE34" s="54"/>
+      <c r="AF34" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG34" s="25"/>
-      <c r="AH34" s="25"/>
-      <c r="AI34" s="26"/>
-      <c r="AJ34" s="27">
+      <c r="AG34" s="51"/>
+      <c r="AH34" s="51"/>
+      <c r="AI34" s="52"/>
+      <c r="AJ34" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK34" s="27"/>
-      <c r="AL34" s="27"/>
-      <c r="AM34" s="27"/>
+      <c r="AK34" s="53"/>
+      <c r="AL34" s="53"/>
+      <c r="AM34" s="53"/>
     </row>
     <row r="35" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
+      <c r="A35" s="54"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
-      <c r="O35" s="24">
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+      <c r="N35" s="55"/>
+      <c r="O35" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="30"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="28"/>
-      <c r="AE35" s="28"/>
-      <c r="AF35" s="24">
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="56"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="54"/>
+      <c r="Y35" s="54"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54"/>
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="54"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="54"/>
+      <c r="AF35" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG35" s="25"/>
-      <c r="AH35" s="25"/>
-      <c r="AI35" s="26"/>
-      <c r="AJ35" s="27">
+      <c r="AG35" s="51"/>
+      <c r="AH35" s="51"/>
+      <c r="AI35" s="52"/>
+      <c r="AJ35" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK35" s="27"/>
-      <c r="AL35" s="27"/>
-      <c r="AM35" s="27"/>
+      <c r="AK35" s="53"/>
+      <c r="AL35" s="53"/>
+      <c r="AM35" s="53"/>
     </row>
     <row r="36" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="24">
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="30"/>
-      <c r="T36" s="31"/>
-      <c r="U36" s="31"/>
-      <c r="V36" s="31"/>
-      <c r="W36" s="32"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
-      <c r="AD36" s="28"/>
-      <c r="AE36" s="28"/>
-      <c r="AF36" s="24">
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="57"/>
+      <c r="V36" s="57"/>
+      <c r="W36" s="58"/>
+      <c r="X36" s="54"/>
+      <c r="Y36" s="54"/>
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="54"/>
+      <c r="AB36" s="54"/>
+      <c r="AC36" s="54"/>
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="54"/>
+      <c r="AF36" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG36" s="25"/>
-      <c r="AH36" s="25"/>
-      <c r="AI36" s="26"/>
-      <c r="AJ36" s="27">
+      <c r="AG36" s="51"/>
+      <c r="AH36" s="51"/>
+      <c r="AI36" s="52"/>
+      <c r="AJ36" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK36" s="27"/>
-      <c r="AL36" s="27"/>
-      <c r="AM36" s="27"/>
+      <c r="AK36" s="53"/>
+      <c r="AL36" s="53"/>
+      <c r="AM36" s="53"/>
     </row>
     <row r="37" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="24">
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
+      <c r="K37" s="54"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="55"/>
+      <c r="O37" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="32"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
-      <c r="AE37" s="28"/>
-      <c r="AF37" s="24">
+      <c r="P37" s="51"/>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="54"/>
+      <c r="Z37" s="54"/>
+      <c r="AA37" s="54"/>
+      <c r="AB37" s="54"/>
+      <c r="AC37" s="54"/>
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="54"/>
+      <c r="AF37" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG37" s="25"/>
-      <c r="AH37" s="25"/>
-      <c r="AI37" s="26"/>
-      <c r="AJ37" s="27">
+      <c r="AG37" s="51"/>
+      <c r="AH37" s="51"/>
+      <c r="AI37" s="52"/>
+      <c r="AJ37" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK37" s="27"/>
-      <c r="AL37" s="27"/>
-      <c r="AM37" s="27"/>
+      <c r="AK37" s="53"/>
+      <c r="AL37" s="53"/>
+      <c r="AM37" s="53"/>
     </row>
     <row r="38" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="24">
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="55"/>
+      <c r="O38" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="31"/>
-      <c r="U38" s="31"/>
-      <c r="V38" s="31"/>
-      <c r="W38" s="32"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
-      <c r="AD38" s="28"/>
-      <c r="AE38" s="28"/>
-      <c r="AF38" s="24">
+      <c r="P38" s="51"/>
+      <c r="Q38" s="51"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="57"/>
+      <c r="V38" s="57"/>
+      <c r="W38" s="58"/>
+      <c r="X38" s="54"/>
+      <c r="Y38" s="54"/>
+      <c r="Z38" s="54"/>
+      <c r="AA38" s="54"/>
+      <c r="AB38" s="54"/>
+      <c r="AC38" s="54"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="54"/>
+      <c r="AF38" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG38" s="25"/>
-      <c r="AH38" s="25"/>
-      <c r="AI38" s="26"/>
-      <c r="AJ38" s="27">
+      <c r="AG38" s="51"/>
+      <c r="AH38" s="51"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK38" s="27"/>
-      <c r="AL38" s="27"/>
-      <c r="AM38" s="27"/>
+      <c r="AK38" s="53"/>
+      <c r="AL38" s="53"/>
+      <c r="AM38" s="53"/>
     </row>
     <row r="39" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="29"/>
-      <c r="O39" s="24">
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="55"/>
+      <c r="O39" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="30"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="32"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
-      <c r="AD39" s="28"/>
-      <c r="AE39" s="28"/>
-      <c r="AF39" s="24">
+      <c r="P39" s="51"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="57"/>
+      <c r="V39" s="57"/>
+      <c r="W39" s="58"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
+      <c r="Z39" s="54"/>
+      <c r="AA39" s="54"/>
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="54"/>
+      <c r="AF39" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="26"/>
-      <c r="AJ39" s="27">
+      <c r="AG39" s="51"/>
+      <c r="AH39" s="51"/>
+      <c r="AI39" s="52"/>
+      <c r="AJ39" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK39" s="27"/>
-      <c r="AL39" s="27"/>
-      <c r="AM39" s="27"/>
+      <c r="AK39" s="53"/>
+      <c r="AL39" s="53"/>
+      <c r="AM39" s="53"/>
     </row>
     <row r="40" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
+      <c r="A40" s="54"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="24">
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="55"/>
+      <c r="O40" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="26"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
-      <c r="W40" s="32"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
-      <c r="AD40" s="28"/>
-      <c r="AE40" s="28"/>
-      <c r="AF40" s="24">
+      <c r="P40" s="51"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="57"/>
+      <c r="V40" s="57"/>
+      <c r="W40" s="58"/>
+      <c r="X40" s="54"/>
+      <c r="Y40" s="54"/>
+      <c r="Z40" s="54"/>
+      <c r="AA40" s="54"/>
+      <c r="AB40" s="54"/>
+      <c r="AC40" s="54"/>
+      <c r="AD40" s="54"/>
+      <c r="AE40" s="54"/>
+      <c r="AF40" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="26"/>
-      <c r="AJ40" s="27">
+      <c r="AG40" s="51"/>
+      <c r="AH40" s="51"/>
+      <c r="AI40" s="52"/>
+      <c r="AJ40" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK40" s="27"/>
-      <c r="AL40" s="27"/>
-      <c r="AM40" s="27"/>
+      <c r="AK40" s="53"/>
+      <c r="AL40" s="53"/>
+      <c r="AM40" s="53"/>
     </row>
     <row r="41" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="24">
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="54"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="26"/>
-      <c r="S41" s="30"/>
-      <c r="T41" s="31"/>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="32"/>
-      <c r="X41" s="28"/>
-      <c r="Y41" s="28"/>
-      <c r="Z41" s="28"/>
-      <c r="AA41" s="28"/>
-      <c r="AB41" s="28"/>
-      <c r="AC41" s="28"/>
-      <c r="AD41" s="28"/>
-      <c r="AE41" s="28"/>
-      <c r="AF41" s="24">
+      <c r="P41" s="51"/>
+      <c r="Q41" s="51"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="56"/>
+      <c r="T41" s="57"/>
+      <c r="U41" s="57"/>
+      <c r="V41" s="57"/>
+      <c r="W41" s="58"/>
+      <c r="X41" s="54"/>
+      <c r="Y41" s="54"/>
+      <c r="Z41" s="54"/>
+      <c r="AA41" s="54"/>
+      <c r="AB41" s="54"/>
+      <c r="AC41" s="54"/>
+      <c r="AD41" s="54"/>
+      <c r="AE41" s="54"/>
+      <c r="AF41" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="26"/>
-      <c r="AJ41" s="27">
+      <c r="AG41" s="51"/>
+      <c r="AH41" s="51"/>
+      <c r="AI41" s="52"/>
+      <c r="AJ41" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK41" s="27"/>
-      <c r="AL41" s="27"/>
-      <c r="AM41" s="27"/>
+      <c r="AK41" s="53"/>
+      <c r="AL41" s="53"/>
+      <c r="AM41" s="53"/>
     </row>
     <row r="42" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
       <c r="F42" s="2"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29"/>
-      <c r="N42" s="29"/>
-      <c r="O42" s="24">
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P42" s="25"/>
-      <c r="Q42" s="25"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="30"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="32"/>
-      <c r="X42" s="28"/>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
-      <c r="AC42" s="28"/>
-      <c r="AD42" s="28"/>
-      <c r="AE42" s="28"/>
-      <c r="AF42" s="24">
+      <c r="P42" s="51"/>
+      <c r="Q42" s="51"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="57"/>
+      <c r="U42" s="57"/>
+      <c r="V42" s="57"/>
+      <c r="W42" s="58"/>
+      <c r="X42" s="54"/>
+      <c r="Y42" s="54"/>
+      <c r="Z42" s="54"/>
+      <c r="AA42" s="54"/>
+      <c r="AB42" s="54"/>
+      <c r="AC42" s="54"/>
+      <c r="AD42" s="54"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG42" s="25"/>
-      <c r="AH42" s="25"/>
-      <c r="AI42" s="26"/>
-      <c r="AJ42" s="27">
+      <c r="AG42" s="51"/>
+      <c r="AH42" s="51"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK42" s="27"/>
-      <c r="AL42" s="27"/>
-      <c r="AM42" s="27"/>
+      <c r="AK42" s="53"/>
+      <c r="AL42" s="53"/>
+      <c r="AM42" s="53"/>
     </row>
     <row r="43" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="24">
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54"/>
+      <c r="K43" s="54"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P43" s="25"/>
-      <c r="Q43" s="25"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
-      <c r="W43" s="32"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="28"/>
-      <c r="AB43" s="28"/>
-      <c r="AC43" s="28"/>
-      <c r="AD43" s="28"/>
-      <c r="AE43" s="28"/>
-      <c r="AF43" s="24">
+      <c r="P43" s="51"/>
+      <c r="Q43" s="51"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="56"/>
+      <c r="T43" s="57"/>
+      <c r="U43" s="57"/>
+      <c r="V43" s="57"/>
+      <c r="W43" s="58"/>
+      <c r="X43" s="54"/>
+      <c r="Y43" s="54"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="54"/>
+      <c r="AB43" s="54"/>
+      <c r="AC43" s="54"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG43" s="25"/>
-      <c r="AH43" s="25"/>
-      <c r="AI43" s="26"/>
-      <c r="AJ43" s="27">
+      <c r="AG43" s="51"/>
+      <c r="AH43" s="51"/>
+      <c r="AI43" s="52"/>
+      <c r="AJ43" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK43" s="27"/>
-      <c r="AL43" s="27"/>
-      <c r="AM43" s="27"/>
+      <c r="AK43" s="53"/>
+      <c r="AL43" s="53"/>
+      <c r="AM43" s="53"/>
     </row>
     <row r="44" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="24">
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="54"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P44" s="25"/>
-      <c r="Q44" s="25"/>
-      <c r="R44" s="26"/>
-      <c r="S44" s="30"/>
-      <c r="T44" s="31"/>
-      <c r="U44" s="31"/>
-      <c r="V44" s="31"/>
-      <c r="W44" s="32"/>
-      <c r="X44" s="28"/>
-      <c r="Y44" s="28"/>
-      <c r="Z44" s="28"/>
-      <c r="AA44" s="28"/>
-      <c r="AB44" s="28"/>
-      <c r="AC44" s="28"/>
-      <c r="AD44" s="28"/>
-      <c r="AE44" s="28"/>
-      <c r="AF44" s="24">
+      <c r="P44" s="51"/>
+      <c r="Q44" s="51"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="57"/>
+      <c r="U44" s="57"/>
+      <c r="V44" s="57"/>
+      <c r="W44" s="58"/>
+      <c r="X44" s="54"/>
+      <c r="Y44" s="54"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="54"/>
+      <c r="AB44" s="54"/>
+      <c r="AC44" s="54"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG44" s="25"/>
-      <c r="AH44" s="25"/>
-      <c r="AI44" s="26"/>
-      <c r="AJ44" s="27">
+      <c r="AG44" s="51"/>
+      <c r="AH44" s="51"/>
+      <c r="AI44" s="52"/>
+      <c r="AJ44" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK44" s="27"/>
-      <c r="AL44" s="27"/>
-      <c r="AM44" s="27"/>
+      <c r="AK44" s="53"/>
+      <c r="AL44" s="53"/>
+      <c r="AM44" s="53"/>
     </row>
     <row r="45" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="24">
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P45" s="25"/>
-      <c r="Q45" s="25"/>
-      <c r="R45" s="26"/>
-      <c r="S45" s="30"/>
-      <c r="T45" s="31"/>
-      <c r="U45" s="31"/>
-      <c r="V45" s="31"/>
-      <c r="W45" s="32"/>
-      <c r="X45" s="28"/>
-      <c r="Y45" s="28"/>
-      <c r="Z45" s="28"/>
-      <c r="AA45" s="28"/>
-      <c r="AB45" s="28"/>
-      <c r="AC45" s="28"/>
-      <c r="AD45" s="28"/>
-      <c r="AE45" s="28"/>
-      <c r="AF45" s="24">
+      <c r="P45" s="51"/>
+      <c r="Q45" s="51"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="56"/>
+      <c r="T45" s="57"/>
+      <c r="U45" s="57"/>
+      <c r="V45" s="57"/>
+      <c r="W45" s="58"/>
+      <c r="X45" s="54"/>
+      <c r="Y45" s="54"/>
+      <c r="Z45" s="54"/>
+      <c r="AA45" s="54"/>
+      <c r="AB45" s="54"/>
+      <c r="AC45" s="54"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG45" s="25"/>
-      <c r="AH45" s="25"/>
-      <c r="AI45" s="26"/>
-      <c r="AJ45" s="27">
+      <c r="AG45" s="51"/>
+      <c r="AH45" s="51"/>
+      <c r="AI45" s="52"/>
+      <c r="AJ45" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK45" s="27"/>
-      <c r="AL45" s="27"/>
-      <c r="AM45" s="27"/>
+      <c r="AK45" s="53"/>
+      <c r="AL45" s="53"/>
+      <c r="AM45" s="53"/>
     </row>
     <row r="46" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="24">
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P46" s="25"/>
-      <c r="Q46" s="25"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="32"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
-      <c r="AD46" s="28"/>
-      <c r="AE46" s="28"/>
-      <c r="AF46" s="24">
+      <c r="P46" s="51"/>
+      <c r="Q46" s="51"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="56"/>
+      <c r="T46" s="57"/>
+      <c r="U46" s="57"/>
+      <c r="V46" s="57"/>
+      <c r="W46" s="58"/>
+      <c r="X46" s="54"/>
+      <c r="Y46" s="54"/>
+      <c r="Z46" s="54"/>
+      <c r="AA46" s="54"/>
+      <c r="AB46" s="54"/>
+      <c r="AC46" s="54"/>
+      <c r="AD46" s="54"/>
+      <c r="AE46" s="54"/>
+      <c r="AF46" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG46" s="25"/>
-      <c r="AH46" s="25"/>
-      <c r="AI46" s="26"/>
-      <c r="AJ46" s="27">
+      <c r="AG46" s="51"/>
+      <c r="AH46" s="51"/>
+      <c r="AI46" s="52"/>
+      <c r="AJ46" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK46" s="27"/>
-      <c r="AL46" s="27"/>
-      <c r="AM46" s="27"/>
+      <c r="AK46" s="53"/>
+      <c r="AL46" s="53"/>
+      <c r="AM46" s="53"/>
     </row>
     <row r="47" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
       <c r="F47" s="2"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="24">
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="54"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="55"/>
+      <c r="N47" s="55"/>
+      <c r="O47" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P47" s="25"/>
-      <c r="Q47" s="25"/>
-      <c r="R47" s="26"/>
-      <c r="S47" s="30"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="28"/>
-      <c r="Y47" s="28"/>
-      <c r="Z47" s="28"/>
-      <c r="AA47" s="28"/>
-      <c r="AB47" s="28"/>
-      <c r="AC47" s="28"/>
-      <c r="AD47" s="28"/>
-      <c r="AE47" s="28"/>
-      <c r="AF47" s="24">
+      <c r="P47" s="51"/>
+      <c r="Q47" s="51"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="56"/>
+      <c r="T47" s="57"/>
+      <c r="U47" s="57"/>
+      <c r="V47" s="57"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="54"/>
+      <c r="Y47" s="54"/>
+      <c r="Z47" s="54"/>
+      <c r="AA47" s="54"/>
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="54"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="54"/>
+      <c r="AF47" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG47" s="25"/>
-      <c r="AH47" s="25"/>
-      <c r="AI47" s="26"/>
-      <c r="AJ47" s="27">
+      <c r="AG47" s="51"/>
+      <c r="AH47" s="51"/>
+      <c r="AI47" s="52"/>
+      <c r="AJ47" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK47" s="27"/>
-      <c r="AL47" s="27"/>
-      <c r="AM47" s="27"/>
+      <c r="AK47" s="53"/>
+      <c r="AL47" s="53"/>
+      <c r="AM47" s="53"/>
     </row>
     <row r="48" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="24">
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="55"/>
+      <c r="O48" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P48" s="25"/>
-      <c r="Q48" s="25"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="30"/>
-      <c r="T48" s="31"/>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="32"/>
-      <c r="X48" s="28"/>
-      <c r="Y48" s="28"/>
-      <c r="Z48" s="28"/>
-      <c r="AA48" s="28"/>
-      <c r="AB48" s="28"/>
-      <c r="AC48" s="28"/>
-      <c r="AD48" s="28"/>
-      <c r="AE48" s="28"/>
-      <c r="AF48" s="24">
+      <c r="P48" s="51"/>
+      <c r="Q48" s="51"/>
+      <c r="R48" s="52"/>
+      <c r="S48" s="56"/>
+      <c r="T48" s="57"/>
+      <c r="U48" s="57"/>
+      <c r="V48" s="57"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="54"/>
+      <c r="Y48" s="54"/>
+      <c r="Z48" s="54"/>
+      <c r="AA48" s="54"/>
+      <c r="AB48" s="54"/>
+      <c r="AC48" s="54"/>
+      <c r="AD48" s="54"/>
+      <c r="AE48" s="54"/>
+      <c r="AF48" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG48" s="25"/>
-      <c r="AH48" s="25"/>
-      <c r="AI48" s="26"/>
-      <c r="AJ48" s="27">
+      <c r="AG48" s="51"/>
+      <c r="AH48" s="51"/>
+      <c r="AI48" s="52"/>
+      <c r="AJ48" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK48" s="27"/>
-      <c r="AL48" s="27"/>
-      <c r="AM48" s="27"/>
+      <c r="AK48" s="53"/>
+      <c r="AL48" s="53"/>
+      <c r="AM48" s="53"/>
     </row>
     <row r="49" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="24">
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P49" s="25"/>
-      <c r="Q49" s="25"/>
-      <c r="R49" s="26"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="31"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="32"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
-      <c r="AD49" s="28"/>
-      <c r="AE49" s="28"/>
-      <c r="AF49" s="24">
+      <c r="P49" s="51"/>
+      <c r="Q49" s="51"/>
+      <c r="R49" s="52"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="57"/>
+      <c r="U49" s="57"/>
+      <c r="V49" s="57"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="54"/>
+      <c r="Y49" s="54"/>
+      <c r="Z49" s="54"/>
+      <c r="AA49" s="54"/>
+      <c r="AB49" s="54"/>
+      <c r="AC49" s="54"/>
+      <c r="AD49" s="54"/>
+      <c r="AE49" s="54"/>
+      <c r="AF49" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG49" s="25"/>
-      <c r="AH49" s="25"/>
-      <c r="AI49" s="26"/>
-      <c r="AJ49" s="27">
+      <c r="AG49" s="51"/>
+      <c r="AH49" s="51"/>
+      <c r="AI49" s="52"/>
+      <c r="AJ49" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK49" s="27"/>
-      <c r="AL49" s="27"/>
-      <c r="AM49" s="27"/>
+      <c r="AK49" s="53"/>
+      <c r="AL49" s="53"/>
+      <c r="AM49" s="53"/>
     </row>
     <row r="50" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
       <c r="F50" s="2"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="29"/>
-      <c r="M50" s="29"/>
-      <c r="N50" s="29"/>
-      <c r="O50" s="24">
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="55"/>
+      <c r="N50" s="55"/>
+      <c r="O50" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P50" s="25"/>
-      <c r="Q50" s="25"/>
-      <c r="R50" s="26"/>
-      <c r="S50" s="30"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="32"/>
-      <c r="X50" s="28"/>
-      <c r="Y50" s="28"/>
-      <c r="Z50" s="28"/>
-      <c r="AA50" s="28"/>
-      <c r="AB50" s="28"/>
-      <c r="AC50" s="28"/>
-      <c r="AD50" s="28"/>
-      <c r="AE50" s="28"/>
-      <c r="AF50" s="24">
+      <c r="P50" s="51"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="52"/>
+      <c r="S50" s="56"/>
+      <c r="T50" s="57"/>
+      <c r="U50" s="57"/>
+      <c r="V50" s="57"/>
+      <c r="W50" s="58"/>
+      <c r="X50" s="54"/>
+      <c r="Y50" s="54"/>
+      <c r="Z50" s="54"/>
+      <c r="AA50" s="54"/>
+      <c r="AB50" s="54"/>
+      <c r="AC50" s="54"/>
+      <c r="AD50" s="54"/>
+      <c r="AE50" s="54"/>
+      <c r="AF50" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG50" s="25"/>
-      <c r="AH50" s="25"/>
-      <c r="AI50" s="26"/>
-      <c r="AJ50" s="27">
+      <c r="AG50" s="51"/>
+      <c r="AH50" s="51"/>
+      <c r="AI50" s="52"/>
+      <c r="AJ50" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK50" s="27"/>
-      <c r="AL50" s="27"/>
-      <c r="AM50" s="27"/>
+      <c r="AK50" s="53"/>
+      <c r="AL50" s="53"/>
+      <c r="AM50" s="53"/>
     </row>
     <row r="51" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="28"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
+      <c r="A51" s="54"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="24">
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="55"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P51" s="25"/>
-      <c r="Q51" s="25"/>
-      <c r="R51" s="26"/>
-      <c r="S51" s="30"/>
-      <c r="T51" s="31"/>
-      <c r="U51" s="31"/>
-      <c r="V51" s="31"/>
-      <c r="W51" s="32"/>
-      <c r="X51" s="28"/>
-      <c r="Y51" s="28"/>
-      <c r="Z51" s="28"/>
-      <c r="AA51" s="28"/>
-      <c r="AB51" s="28"/>
-      <c r="AC51" s="28"/>
-      <c r="AD51" s="28"/>
-      <c r="AE51" s="28"/>
-      <c r="AF51" s="24">
+      <c r="P51" s="51"/>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="52"/>
+      <c r="S51" s="56"/>
+      <c r="T51" s="57"/>
+      <c r="U51" s="57"/>
+      <c r="V51" s="57"/>
+      <c r="W51" s="58"/>
+      <c r="X51" s="54"/>
+      <c r="Y51" s="54"/>
+      <c r="Z51" s="54"/>
+      <c r="AA51" s="54"/>
+      <c r="AB51" s="54"/>
+      <c r="AC51" s="54"/>
+      <c r="AD51" s="54"/>
+      <c r="AE51" s="54"/>
+      <c r="AF51" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG51" s="25"/>
-      <c r="AH51" s="25"/>
-      <c r="AI51" s="26"/>
-      <c r="AJ51" s="27">
+      <c r="AG51" s="51"/>
+      <c r="AH51" s="51"/>
+      <c r="AI51" s="52"/>
+      <c r="AJ51" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK51" s="27"/>
-      <c r="AL51" s="27"/>
-      <c r="AM51" s="27"/>
+      <c r="AK51" s="53"/>
+      <c r="AL51" s="53"/>
+      <c r="AM51" s="53"/>
     </row>
     <row r="52" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
+      <c r="A52" s="54"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
       <c r="F52" s="2"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="24">
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="54"/>
+      <c r="K52" s="54"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="55"/>
+      <c r="N52" s="55"/>
+      <c r="O52" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P52" s="25"/>
-      <c r="Q52" s="25"/>
-      <c r="R52" s="26"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
-      <c r="W52" s="32"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="28"/>
-      <c r="AB52" s="28"/>
-      <c r="AC52" s="28"/>
-      <c r="AD52" s="28"/>
-      <c r="AE52" s="28"/>
-      <c r="AF52" s="24">
+      <c r="P52" s="51"/>
+      <c r="Q52" s="51"/>
+      <c r="R52" s="52"/>
+      <c r="S52" s="56"/>
+      <c r="T52" s="57"/>
+      <c r="U52" s="57"/>
+      <c r="V52" s="57"/>
+      <c r="W52" s="58"/>
+      <c r="X52" s="54"/>
+      <c r="Y52" s="54"/>
+      <c r="Z52" s="54"/>
+      <c r="AA52" s="54"/>
+      <c r="AB52" s="54"/>
+      <c r="AC52" s="54"/>
+      <c r="AD52" s="54"/>
+      <c r="AE52" s="54"/>
+      <c r="AF52" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG52" s="25"/>
-      <c r="AH52" s="25"/>
-      <c r="AI52" s="26"/>
-      <c r="AJ52" s="27">
+      <c r="AG52" s="51"/>
+      <c r="AH52" s="51"/>
+      <c r="AI52" s="52"/>
+      <c r="AJ52" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK52" s="27"/>
-      <c r="AL52" s="27"/>
-      <c r="AM52" s="27"/>
+      <c r="AK52" s="53"/>
+      <c r="AL52" s="53"/>
+      <c r="AM52" s="53"/>
     </row>
     <row r="53" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="28"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
       <c r="F53" s="2"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
-      <c r="N53" s="29"/>
-      <c r="O53" s="24">
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="54"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="55"/>
+      <c r="N53" s="55"/>
+      <c r="O53" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P53" s="25"/>
-      <c r="Q53" s="25"/>
-      <c r="R53" s="26"/>
-      <c r="S53" s="30"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="32"/>
-      <c r="X53" s="28"/>
-      <c r="Y53" s="28"/>
-      <c r="Z53" s="28"/>
-      <c r="AA53" s="28"/>
-      <c r="AB53" s="28"/>
-      <c r="AC53" s="28"/>
-      <c r="AD53" s="28"/>
-      <c r="AE53" s="28"/>
-      <c r="AF53" s="24">
+      <c r="P53" s="51"/>
+      <c r="Q53" s="51"/>
+      <c r="R53" s="52"/>
+      <c r="S53" s="56"/>
+      <c r="T53" s="57"/>
+      <c r="U53" s="57"/>
+      <c r="V53" s="57"/>
+      <c r="W53" s="58"/>
+      <c r="X53" s="54"/>
+      <c r="Y53" s="54"/>
+      <c r="Z53" s="54"/>
+      <c r="AA53" s="54"/>
+      <c r="AB53" s="54"/>
+      <c r="AC53" s="54"/>
+      <c r="AD53" s="54"/>
+      <c r="AE53" s="54"/>
+      <c r="AF53" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG53" s="25"/>
-      <c r="AH53" s="25"/>
-      <c r="AI53" s="26"/>
-      <c r="AJ53" s="27">
+      <c r="AG53" s="51"/>
+      <c r="AH53" s="51"/>
+      <c r="AI53" s="52"/>
+      <c r="AJ53" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK53" s="27"/>
-      <c r="AL53" s="27"/>
-      <c r="AM53" s="27"/>
+      <c r="AK53" s="53"/>
+      <c r="AL53" s="53"/>
+      <c r="AM53" s="53"/>
     </row>
     <row r="54" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
+      <c r="A54" s="54"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
       <c r="F54" s="2"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
-      <c r="K54" s="28"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="24">
+      <c r="G54" s="54"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="55"/>
+      <c r="N54" s="55"/>
+      <c r="O54" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P54" s="25"/>
-      <c r="Q54" s="25"/>
-      <c r="R54" s="26"/>
-      <c r="S54" s="30"/>
-      <c r="T54" s="31"/>
-      <c r="U54" s="31"/>
-      <c r="V54" s="31"/>
-      <c r="W54" s="32"/>
-      <c r="X54" s="28"/>
-      <c r="Y54" s="28"/>
-      <c r="Z54" s="28"/>
-      <c r="AA54" s="28"/>
-      <c r="AB54" s="28"/>
-      <c r="AC54" s="28"/>
-      <c r="AD54" s="28"/>
-      <c r="AE54" s="28"/>
-      <c r="AF54" s="24">
+      <c r="P54" s="51"/>
+      <c r="Q54" s="51"/>
+      <c r="R54" s="52"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="57"/>
+      <c r="U54" s="57"/>
+      <c r="V54" s="57"/>
+      <c r="W54" s="58"/>
+      <c r="X54" s="54"/>
+      <c r="Y54" s="54"/>
+      <c r="Z54" s="54"/>
+      <c r="AA54" s="54"/>
+      <c r="AB54" s="54"/>
+      <c r="AC54" s="54"/>
+      <c r="AD54" s="54"/>
+      <c r="AE54" s="54"/>
+      <c r="AF54" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG54" s="25"/>
-      <c r="AH54" s="25"/>
-      <c r="AI54" s="26"/>
-      <c r="AJ54" s="27">
+      <c r="AG54" s="51"/>
+      <c r="AH54" s="51"/>
+      <c r="AI54" s="52"/>
+      <c r="AJ54" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK54" s="27"/>
-      <c r="AL54" s="27"/>
-      <c r="AM54" s="27"/>
+      <c r="AK54" s="53"/>
+      <c r="AL54" s="53"/>
+      <c r="AM54" s="53"/>
     </row>
     <row r="55" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
+      <c r="A55" s="54"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
       <c r="F55" s="2"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="24">
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="55"/>
+      <c r="N55" s="55"/>
+      <c r="O55" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P55" s="25"/>
-      <c r="Q55" s="25"/>
-      <c r="R55" s="26"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="31"/>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
-      <c r="W55" s="32"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
-      <c r="Z55" s="28"/>
-      <c r="AA55" s="28"/>
-      <c r="AB55" s="28"/>
-      <c r="AC55" s="28"/>
-      <c r="AD55" s="28"/>
-      <c r="AE55" s="28"/>
-      <c r="AF55" s="24">
+      <c r="P55" s="51"/>
+      <c r="Q55" s="51"/>
+      <c r="R55" s="52"/>
+      <c r="S55" s="56"/>
+      <c r="T55" s="57"/>
+      <c r="U55" s="57"/>
+      <c r="V55" s="57"/>
+      <c r="W55" s="58"/>
+      <c r="X55" s="54"/>
+      <c r="Y55" s="54"/>
+      <c r="Z55" s="54"/>
+      <c r="AA55" s="54"/>
+      <c r="AB55" s="54"/>
+      <c r="AC55" s="54"/>
+      <c r="AD55" s="54"/>
+      <c r="AE55" s="54"/>
+      <c r="AF55" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG55" s="25"/>
-      <c r="AH55" s="25"/>
-      <c r="AI55" s="26"/>
-      <c r="AJ55" s="27">
+      <c r="AG55" s="51"/>
+      <c r="AH55" s="51"/>
+      <c r="AI55" s="52"/>
+      <c r="AJ55" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK55" s="27"/>
-      <c r="AL55" s="27"/>
-      <c r="AM55" s="27"/>
+      <c r="AK55" s="53"/>
+      <c r="AL55" s="53"/>
+      <c r="AM55" s="53"/>
     </row>
     <row r="56" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
+      <c r="A56" s="54"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
       <c r="F56" s="2"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-      <c r="K56" s="28"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="29"/>
-      <c r="O56" s="24">
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="54"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="55"/>
+      <c r="N56" s="55"/>
+      <c r="O56" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P56" s="25"/>
-      <c r="Q56" s="25"/>
-      <c r="R56" s="26"/>
-      <c r="S56" s="30"/>
-      <c r="T56" s="31"/>
-      <c r="U56" s="31"/>
-      <c r="V56" s="31"/>
-      <c r="W56" s="32"/>
-      <c r="X56" s="28"/>
-      <c r="Y56" s="28"/>
-      <c r="Z56" s="28"/>
-      <c r="AA56" s="28"/>
-      <c r="AB56" s="28"/>
-      <c r="AC56" s="28"/>
-      <c r="AD56" s="28"/>
-      <c r="AE56" s="28"/>
-      <c r="AF56" s="24">
+      <c r="P56" s="51"/>
+      <c r="Q56" s="51"/>
+      <c r="R56" s="52"/>
+      <c r="S56" s="56"/>
+      <c r="T56" s="57"/>
+      <c r="U56" s="57"/>
+      <c r="V56" s="57"/>
+      <c r="W56" s="58"/>
+      <c r="X56" s="54"/>
+      <c r="Y56" s="54"/>
+      <c r="Z56" s="54"/>
+      <c r="AA56" s="54"/>
+      <c r="AB56" s="54"/>
+      <c r="AC56" s="54"/>
+      <c r="AD56" s="54"/>
+      <c r="AE56" s="54"/>
+      <c r="AF56" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG56" s="25"/>
-      <c r="AH56" s="25"/>
-      <c r="AI56" s="26"/>
-      <c r="AJ56" s="27">
+      <c r="AG56" s="51"/>
+      <c r="AH56" s="51"/>
+      <c r="AI56" s="52"/>
+      <c r="AJ56" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK56" s="27"/>
-      <c r="AL56" s="27"/>
-      <c r="AM56" s="27"/>
+      <c r="AK56" s="53"/>
+      <c r="AL56" s="53"/>
+      <c r="AM56" s="53"/>
     </row>
     <row r="57" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
+      <c r="A57" s="54"/>
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
       <c r="F57" s="2"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="24">
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="54"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="55"/>
+      <c r="N57" s="55"/>
+      <c r="O57" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P57" s="25"/>
-      <c r="Q57" s="25"/>
-      <c r="R57" s="26"/>
-      <c r="S57" s="30"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="32"/>
-      <c r="X57" s="28"/>
-      <c r="Y57" s="28"/>
-      <c r="Z57" s="28"/>
-      <c r="AA57" s="28"/>
-      <c r="AB57" s="28"/>
-      <c r="AC57" s="28"/>
-      <c r="AD57" s="28"/>
-      <c r="AE57" s="28"/>
-      <c r="AF57" s="24">
+      <c r="P57" s="51"/>
+      <c r="Q57" s="51"/>
+      <c r="R57" s="52"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="57"/>
+      <c r="U57" s="57"/>
+      <c r="V57" s="57"/>
+      <c r="W57" s="58"/>
+      <c r="X57" s="54"/>
+      <c r="Y57" s="54"/>
+      <c r="Z57" s="54"/>
+      <c r="AA57" s="54"/>
+      <c r="AB57" s="54"/>
+      <c r="AC57" s="54"/>
+      <c r="AD57" s="54"/>
+      <c r="AE57" s="54"/>
+      <c r="AF57" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG57" s="25"/>
-      <c r="AH57" s="25"/>
-      <c r="AI57" s="26"/>
-      <c r="AJ57" s="27">
+      <c r="AG57" s="51"/>
+      <c r="AH57" s="51"/>
+      <c r="AI57" s="52"/>
+      <c r="AJ57" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK57" s="27"/>
-      <c r="AL57" s="27"/>
-      <c r="AM57" s="27"/>
+      <c r="AK57" s="53"/>
+      <c r="AL57" s="53"/>
+      <c r="AM57" s="53"/>
     </row>
     <row r="58" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="28"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
+      <c r="A58" s="54"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="24">
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="54"/>
+      <c r="L58" s="55"/>
+      <c r="M58" s="55"/>
+      <c r="N58" s="55"/>
+      <c r="O58" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P58" s="25"/>
-      <c r="Q58" s="25"/>
-      <c r="R58" s="26"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="32"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
-      <c r="Z58" s="28"/>
-      <c r="AA58" s="28"/>
-      <c r="AB58" s="28"/>
-      <c r="AC58" s="28"/>
-      <c r="AD58" s="28"/>
-      <c r="AE58" s="28"/>
-      <c r="AF58" s="24">
+      <c r="P58" s="51"/>
+      <c r="Q58" s="51"/>
+      <c r="R58" s="52"/>
+      <c r="S58" s="56"/>
+      <c r="T58" s="57"/>
+      <c r="U58" s="57"/>
+      <c r="V58" s="57"/>
+      <c r="W58" s="58"/>
+      <c r="X58" s="54"/>
+      <c r="Y58" s="54"/>
+      <c r="Z58" s="54"/>
+      <c r="AA58" s="54"/>
+      <c r="AB58" s="54"/>
+      <c r="AC58" s="54"/>
+      <c r="AD58" s="54"/>
+      <c r="AE58" s="54"/>
+      <c r="AF58" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG58" s="25"/>
-      <c r="AH58" s="25"/>
-      <c r="AI58" s="26"/>
-      <c r="AJ58" s="27">
+      <c r="AG58" s="51"/>
+      <c r="AH58" s="51"/>
+      <c r="AI58" s="52"/>
+      <c r="AJ58" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK58" s="27"/>
-      <c r="AL58" s="27"/>
-      <c r="AM58" s="27"/>
+      <c r="AK58" s="53"/>
+      <c r="AL58" s="53"/>
+      <c r="AM58" s="53"/>
     </row>
     <row r="59" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
+      <c r="A59" s="54"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
       <c r="F59" s="2"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="29"/>
-      <c r="M59" s="29"/>
-      <c r="N59" s="29"/>
-      <c r="O59" s="24">
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="54"/>
+      <c r="L59" s="55"/>
+      <c r="M59" s="55"/>
+      <c r="N59" s="55"/>
+      <c r="O59" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P59" s="25"/>
-      <c r="Q59" s="25"/>
-      <c r="R59" s="26"/>
-      <c r="S59" s="30"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="32"/>
-      <c r="X59" s="28"/>
-      <c r="Y59" s="28"/>
-      <c r="Z59" s="28"/>
-      <c r="AA59" s="28"/>
-      <c r="AB59" s="28"/>
-      <c r="AC59" s="28"/>
-      <c r="AD59" s="28"/>
-      <c r="AE59" s="28"/>
-      <c r="AF59" s="24">
+      <c r="P59" s="51"/>
+      <c r="Q59" s="51"/>
+      <c r="R59" s="52"/>
+      <c r="S59" s="56"/>
+      <c r="T59" s="57"/>
+      <c r="U59" s="57"/>
+      <c r="V59" s="57"/>
+      <c r="W59" s="58"/>
+      <c r="X59" s="54"/>
+      <c r="Y59" s="54"/>
+      <c r="Z59" s="54"/>
+      <c r="AA59" s="54"/>
+      <c r="AB59" s="54"/>
+      <c r="AC59" s="54"/>
+      <c r="AD59" s="54"/>
+      <c r="AE59" s="54"/>
+      <c r="AF59" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG59" s="25"/>
-      <c r="AH59" s="25"/>
-      <c r="AI59" s="26"/>
-      <c r="AJ59" s="27">
+      <c r="AG59" s="51"/>
+      <c r="AH59" s="51"/>
+      <c r="AI59" s="52"/>
+      <c r="AJ59" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK59" s="27"/>
-      <c r="AL59" s="27"/>
-      <c r="AM59" s="27"/>
+      <c r="AK59" s="53"/>
+      <c r="AL59" s="53"/>
+      <c r="AM59" s="53"/>
     </row>
     <row r="60" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
+      <c r="A60" s="54"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="24">
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="55"/>
+      <c r="M60" s="55"/>
+      <c r="N60" s="55"/>
+      <c r="O60" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P60" s="25"/>
-      <c r="Q60" s="25"/>
-      <c r="R60" s="26"/>
-      <c r="S60" s="30"/>
-      <c r="T60" s="31"/>
-      <c r="U60" s="31"/>
-      <c r="V60" s="31"/>
-      <c r="W60" s="32"/>
-      <c r="X60" s="28"/>
-      <c r="Y60" s="28"/>
-      <c r="Z60" s="28"/>
-      <c r="AA60" s="28"/>
-      <c r="AB60" s="28"/>
-      <c r="AC60" s="28"/>
-      <c r="AD60" s="28"/>
-      <c r="AE60" s="28"/>
-      <c r="AF60" s="24">
+      <c r="P60" s="51"/>
+      <c r="Q60" s="51"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="56"/>
+      <c r="T60" s="57"/>
+      <c r="U60" s="57"/>
+      <c r="V60" s="57"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="54"/>
+      <c r="Y60" s="54"/>
+      <c r="Z60" s="54"/>
+      <c r="AA60" s="54"/>
+      <c r="AB60" s="54"/>
+      <c r="AC60" s="54"/>
+      <c r="AD60" s="54"/>
+      <c r="AE60" s="54"/>
+      <c r="AF60" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG60" s="25"/>
-      <c r="AH60" s="25"/>
-      <c r="AI60" s="26"/>
-      <c r="AJ60" s="27">
+      <c r="AG60" s="51"/>
+      <c r="AH60" s="51"/>
+      <c r="AI60" s="52"/>
+      <c r="AJ60" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK60" s="27"/>
-      <c r="AL60" s="27"/>
-      <c r="AM60" s="27"/>
+      <c r="AK60" s="53"/>
+      <c r="AL60" s="53"/>
+      <c r="AM60" s="53"/>
     </row>
     <row r="61" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
+      <c r="A61" s="54"/>
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
       <c r="F61" s="2"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="24">
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="54"/>
+      <c r="L61" s="55"/>
+      <c r="M61" s="55"/>
+      <c r="N61" s="55"/>
+      <c r="O61" s="50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P61" s="25"/>
-      <c r="Q61" s="25"/>
-      <c r="R61" s="26"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="32"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
-      <c r="AD61" s="28"/>
-      <c r="AE61" s="28"/>
-      <c r="AF61" s="24">
+      <c r="P61" s="51"/>
+      <c r="Q61" s="51"/>
+      <c r="R61" s="52"/>
+      <c r="S61" s="56"/>
+      <c r="T61" s="57"/>
+      <c r="U61" s="57"/>
+      <c r="V61" s="57"/>
+      <c r="W61" s="58"/>
+      <c r="X61" s="54"/>
+      <c r="Y61" s="54"/>
+      <c r="Z61" s="54"/>
+      <c r="AA61" s="54"/>
+      <c r="AB61" s="54"/>
+      <c r="AC61" s="54"/>
+      <c r="AD61" s="54"/>
+      <c r="AE61" s="54"/>
+      <c r="AF61" s="50">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG61" s="25"/>
-      <c r="AH61" s="25"/>
-      <c r="AI61" s="26"/>
-      <c r="AJ61" s="27">
+      <c r="AG61" s="51"/>
+      <c r="AH61" s="51"/>
+      <c r="AI61" s="52"/>
+      <c r="AJ61" s="53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK61" s="27"/>
-      <c r="AL61" s="27"/>
-      <c r="AM61" s="27"/>
+      <c r="AK61" s="53"/>
+      <c r="AL61" s="53"/>
+      <c r="AM61" s="53"/>
     </row>
     <row r="62" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="28"/>
-      <c r="E62" s="28"/>
+      <c r="A62" s="54"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
       <c r="F62" s="2"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28"/>
-      <c r="J62" s="28"/>
-      <c r="K62" s="28"/>
-      <c r="L62" s="29"/>
-      <c r="M62" s="29"/>
-      <c r="N62" s="29"/>
-      <c r="O62" s="24">
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="55"/>
+      <c r="M62" s="55"/>
+      <c r="N62" s="55"/>
+      <c r="O62" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P62" s="25"/>
-      <c r="Q62" s="25"/>
-      <c r="R62" s="26"/>
-      <c r="S62" s="30"/>
-      <c r="T62" s="31"/>
-      <c r="U62" s="31"/>
-      <c r="V62" s="31"/>
-      <c r="W62" s="32"/>
-      <c r="X62" s="28"/>
-      <c r="Y62" s="28"/>
-      <c r="Z62" s="28"/>
-      <c r="AA62" s="28"/>
-      <c r="AB62" s="28"/>
-      <c r="AC62" s="28"/>
-      <c r="AD62" s="28"/>
-      <c r="AE62" s="28"/>
-      <c r="AF62" s="24">
+      <c r="P62" s="51"/>
+      <c r="Q62" s="51"/>
+      <c r="R62" s="52"/>
+      <c r="S62" s="56"/>
+      <c r="T62" s="57"/>
+      <c r="U62" s="57"/>
+      <c r="V62" s="57"/>
+      <c r="W62" s="58"/>
+      <c r="X62" s="54"/>
+      <c r="Y62" s="54"/>
+      <c r="Z62" s="54"/>
+      <c r="AA62" s="54"/>
+      <c r="AB62" s="54"/>
+      <c r="AC62" s="54"/>
+      <c r="AD62" s="54"/>
+      <c r="AE62" s="54"/>
+      <c r="AF62" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG62" s="25"/>
-      <c r="AH62" s="25"/>
-      <c r="AI62" s="26"/>
-      <c r="AJ62" s="27">
+      <c r="AG62" s="51"/>
+      <c r="AH62" s="51"/>
+      <c r="AI62" s="52"/>
+      <c r="AJ62" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK62" s="27"/>
-      <c r="AL62" s="27"/>
-      <c r="AM62" s="27"/>
+      <c r="AK62" s="53"/>
+      <c r="AL62" s="53"/>
+      <c r="AM62" s="53"/>
     </row>
     <row r="63" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="28"/>
-      <c r="E63" s="28"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
       <c r="F63" s="2"/>
-      <c r="G63" s="36">
+      <c r="G63" s="62">
         <f>SUM(G6:G62)</f>
         <v>0</v>
       </c>
-      <c r="H63" s="36"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="28"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="58">
+      <c r="H63" s="62"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="54"/>
+      <c r="L63" s="55"/>
+      <c r="M63" s="55"/>
+      <c r="N63" s="55"/>
+      <c r="O63" s="79">
         <f>SUM(O6:O62)</f>
         <v>0</v>
       </c>
-      <c r="P63" s="59"/>
-      <c r="Q63" s="59"/>
-      <c r="R63" s="60"/>
-      <c r="S63" s="30"/>
-      <c r="T63" s="31"/>
-      <c r="U63" s="31"/>
-      <c r="V63" s="31"/>
-      <c r="W63" s="32"/>
-      <c r="X63" s="28"/>
-      <c r="Y63" s="28"/>
-      <c r="Z63" s="28"/>
-      <c r="AA63" s="28"/>
-      <c r="AB63" s="28"/>
-      <c r="AC63" s="28"/>
-      <c r="AD63" s="28"/>
-      <c r="AE63" s="28"/>
-      <c r="AF63" s="58">
+      <c r="P63" s="80"/>
+      <c r="Q63" s="80"/>
+      <c r="R63" s="81"/>
+      <c r="S63" s="56"/>
+      <c r="T63" s="57"/>
+      <c r="U63" s="57"/>
+      <c r="V63" s="57"/>
+      <c r="W63" s="58"/>
+      <c r="X63" s="54"/>
+      <c r="Y63" s="54"/>
+      <c r="Z63" s="54"/>
+      <c r="AA63" s="54"/>
+      <c r="AB63" s="54"/>
+      <c r="AC63" s="54"/>
+      <c r="AD63" s="54"/>
+      <c r="AE63" s="54"/>
+      <c r="AF63" s="79">
         <f>SUM(AF6:AF62)</f>
         <v>0</v>
       </c>
-      <c r="AG63" s="59"/>
-      <c r="AH63" s="59"/>
-      <c r="AI63" s="60"/>
-      <c r="AJ63" s="58">
+      <c r="AG63" s="80"/>
+      <c r="AH63" s="80"/>
+      <c r="AI63" s="81"/>
+      <c r="AJ63" s="79">
         <f>SUM(AJ6:AJ62)</f>
         <v>0</v>
       </c>
-      <c r="AK63" s="59"/>
-      <c r="AL63" s="59"/>
-      <c r="AM63" s="60"/>
+      <c r="AK63" s="80"/>
+      <c r="AL63" s="80"/>
+      <c r="AM63" s="81"/>
     </row>
     <row r="64" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="9" t="s">
@@ -6581,21 +6576,21 @@
       <c r="I1" s="12"/>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
-      <c r="L1" s="98" t="s">
+      <c r="L1" s="97" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
       <c r="Y1" s="12"/>
       <c r="Z1" s="12"/>
       <c r="AA1" s="12"/>
@@ -6611,43 +6606,43 @@
       </c>
     </row>
     <row r="2" spans="1:37" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Y2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="82"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="82"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="82"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
+      <c r="AE2" s="82"/>
+      <c r="AF2" s="82"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="82"/>
+      <c r="AI2" s="82"/>
     </row>
     <row r="3" spans="1:37" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="12"/>
@@ -6664,213 +6659,213 @@
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
-      <c r="O3" s="84" t="s">
+      <c r="O3" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84">
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83">
         <v>99</v>
       </c>
-      <c r="S3" s="84"/>
-      <c r="T3" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="U3" s="84"/>
-      <c r="V3" s="84"/>
-      <c r="W3" s="28" t="s">
+      <c r="S3" s="83"/>
+      <c r="T3" s="83" t="s">
+        <v>0</v>
+      </c>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="84" t="s">
+      <c r="X3" s="54"/>
+      <c r="Y3" s="54"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="AF3" s="84"/>
-      <c r="AG3" s="84"/>
-      <c r="AH3" s="28">
+      <c r="AF3" s="83"/>
+      <c r="AG3" s="83"/>
+      <c r="AH3" s="54">
         <v>1</v>
       </c>
-      <c r="AI3" s="28"/>
+      <c r="AI3" s="54"/>
       <c r="AK3" s="1"/>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.45">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="84"/>
-      <c r="M4" s="84" t="s">
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="84"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="84" t="s">
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="T4" s="84"/>
-      <c r="U4" s="84"/>
-      <c r="V4" s="84"/>
-      <c r="W4" s="84"/>
-      <c r="X4" s="84"/>
-      <c r="Y4" s="85" t="s">
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="Z4" s="86"/>
-      <c r="AA4" s="84" t="s">
+      <c r="Z4" s="85"/>
+      <c r="AA4" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" s="84"/>
-      <c r="AC4" s="84"/>
-      <c r="AD4" s="84"/>
-      <c r="AE4" s="84"/>
-      <c r="AF4" s="84"/>
-      <c r="AG4" s="84"/>
-      <c r="AH4" s="84"/>
-      <c r="AI4" s="84"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="83"/>
     </row>
     <row r="5" spans="1:37" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84" t="s">
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="N5" s="84"/>
-      <c r="O5" s="91" t="s">
+      <c r="N5" s="83"/>
+      <c r="O5" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91" t="s">
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="91"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="87"/>
-      <c r="Z5" s="88"/>
-      <c r="AA5" s="84"/>
-      <c r="AB5" s="84"/>
-      <c r="AC5" s="84"/>
-      <c r="AD5" s="84"/>
-      <c r="AE5" s="84"/>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="83"/>
+      <c r="T5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
+      <c r="W5" s="83"/>
+      <c r="X5" s="83"/>
+      <c r="Y5" s="86"/>
+      <c r="Z5" s="87"/>
+      <c r="AA5" s="83"/>
+      <c r="AB5" s="83"/>
+      <c r="AC5" s="83"/>
+      <c r="AD5" s="83"/>
+      <c r="AE5" s="83"/>
+      <c r="AF5" s="83"/>
+      <c r="AG5" s="83"/>
+      <c r="AH5" s="83"/>
+      <c r="AI5" s="83"/>
     </row>
     <row r="6" spans="1:37" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="84"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84" t="s">
+      <c r="A6" s="83"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84" t="s">
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84" t="s">
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="91"/>
-      <c r="P6" s="91"/>
-      <c r="Q6" s="91"/>
-      <c r="R6" s="91"/>
-      <c r="S6" s="84"/>
-      <c r="T6" s="84"/>
-      <c r="U6" s="84"/>
-      <c r="V6" s="84"/>
-      <c r="W6" s="84"/>
-      <c r="X6" s="84"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="90"/>
-      <c r="AA6" s="84"/>
-      <c r="AB6" s="84"/>
-      <c r="AC6" s="84"/>
-      <c r="AD6" s="84"/>
-      <c r="AE6" s="84"/>
-      <c r="AF6" s="84"/>
-      <c r="AG6" s="84"/>
-      <c r="AH6" s="84"/>
-      <c r="AI6" s="84"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="83"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="88"/>
+      <c r="Z6" s="89"/>
+      <c r="AA6" s="83"/>
+      <c r="AB6" s="83"/>
+      <c r="AC6" s="83"/>
+      <c r="AD6" s="83"/>
+      <c r="AE6" s="83"/>
+      <c r="AF6" s="83"/>
+      <c r="AG6" s="83"/>
+      <c r="AH6" s="83"/>
+      <c r="AI6" s="83"/>
     </row>
     <row r="7" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="107">
+      <c r="A7" s="106">
         <v>46183</v>
       </c>
-      <c r="B7" s="107"/>
-      <c r="C7" s="92">
+      <c r="B7" s="106"/>
+      <c r="C7" s="91">
         <v>0.375</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92">
+      <c r="D7" s="91"/>
+      <c r="E7" s="91"/>
+      <c r="F7" s="91">
         <v>0.45833333333333331</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="36">
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="62">
         <v>2</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="84" t="s">
+      <c r="J7" s="62"/>
+      <c r="K7" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="84"/>
-      <c r="M7" s="28">
+      <c r="L7" s="83"/>
+      <c r="M7" s="54">
         <v>2</v>
       </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28">
+      <c r="N7" s="54"/>
+      <c r="O7" s="54">
         <v>2</v>
       </c>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28">
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54">
         <v>4</v>
       </c>
-      <c r="R7" s="28"/>
+      <c r="R7" s="54"/>
       <c r="S7" s="2">
         <v>7</v>
       </c>
@@ -6881,97 +6876,97 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="28">
+      <c r="Y7" s="54">
         <v>1</v>
       </c>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="100" t="s">
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AB7" s="100"/>
-      <c r="AC7" s="100"/>
-      <c r="AD7" s="100"/>
-      <c r="AE7" s="100"/>
-      <c r="AF7" s="100"/>
-      <c r="AG7" s="100"/>
-      <c r="AH7" s="100"/>
-      <c r="AI7" s="100"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="99"/>
+      <c r="AF7" s="99"/>
+      <c r="AG7" s="99"/>
+      <c r="AH7" s="99"/>
+      <c r="AI7" s="99"/>
     </row>
     <row r="8" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="102"/>
-      <c r="AE8" s="102"/>
-      <c r="AF8" s="102"/>
-      <c r="AG8" s="102"/>
-      <c r="AH8" s="102"/>
-      <c r="AI8" s="103"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="101"/>
+      <c r="L8" s="101"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="101"/>
+      <c r="Q8" s="101"/>
+      <c r="R8" s="101"/>
+      <c r="S8" s="101"/>
+      <c r="T8" s="101"/>
+      <c r="U8" s="101"/>
+      <c r="V8" s="101"/>
+      <c r="W8" s="101"/>
+      <c r="X8" s="101"/>
+      <c r="Y8" s="101"/>
+      <c r="Z8" s="101"/>
+      <c r="AA8" s="101"/>
+      <c r="AB8" s="101"/>
+      <c r="AC8" s="101"/>
+      <c r="AD8" s="101"/>
+      <c r="AE8" s="101"/>
+      <c r="AF8" s="101"/>
+      <c r="AG8" s="101"/>
+      <c r="AH8" s="101"/>
+      <c r="AI8" s="102"/>
     </row>
     <row r="9" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="104"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="105"/>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="105"/>
-      <c r="AC9" s="105"/>
-      <c r="AD9" s="105"/>
-      <c r="AE9" s="105"/>
-      <c r="AF9" s="105"/>
-      <c r="AG9" s="105"/>
-      <c r="AH9" s="105"/>
-      <c r="AI9" s="106"/>
+      <c r="A9" s="103"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="104"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="104"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="104"/>
+      <c r="R9" s="104"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="104"/>
+      <c r="U9" s="104"/>
+      <c r="V9" s="104"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="104"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="104"/>
+      <c r="AA9" s="104"/>
+      <c r="AB9" s="104"/>
+      <c r="AC9" s="104"/>
+      <c r="AD9" s="104"/>
+      <c r="AE9" s="104"/>
+      <c r="AF9" s="104"/>
+      <c r="AG9" s="104"/>
+      <c r="AH9" s="104"/>
+      <c r="AI9" s="105"/>
     </row>
     <row r="10" spans="1:37" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12"/>
@@ -7013,26 +7008,26 @@
       <c r="AI10" s="12"/>
     </row>
     <row r="11" spans="1:37" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="84"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="84"/>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="91" t="s">
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="L11" s="84"/>
-      <c r="M11" s="93" t="s">
+      <c r="L11" s="83"/>
+      <c r="M11" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="94"/>
+      <c r="N11" s="93"/>
       <c r="O11" s="12"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="12"/>
@@ -7061,23 +7056,23 @@
       <c r="A12" s="14">
         <v>1</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="95"/>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="96" t="s">
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="94"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="L12" s="97"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="83"/>
+      <c r="N12" s="83"/>
       <c r="O12" s="12"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="12"/>
@@ -7106,23 +7101,23 @@
       <c r="A13" s="14">
         <v>2</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="95"/>
-      <c r="K13" s="96" t="s">
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="94"/>
+      <c r="J13" s="94"/>
+      <c r="K13" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="L13" s="97"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
+      <c r="L13" s="96"/>
+      <c r="M13" s="83"/>
+      <c r="N13" s="83"/>
       <c r="O13" s="12"/>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
@@ -7151,21 +7146,21 @@
       <c r="A14" s="14">
         <v>3</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="30"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="84"/>
-      <c r="N14" s="84"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="94"/>
+      <c r="J14" s="94"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="83"/>
+      <c r="N14" s="83"/>
       <c r="O14" s="12"/>
       <c r="P14" s="12"/>
       <c r="Q14" s="12"/>
@@ -7192,23 +7187,23 @@
       <c r="A15" s="14">
         <v>4</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="95"/>
-      <c r="F15" s="95"/>
-      <c r="G15" s="95"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="95"/>
-      <c r="J15" s="95"/>
-      <c r="K15" s="96" t="s">
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="97"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="83"/>
+      <c r="N15" s="83"/>
       <c r="O15" s="12"/>
       <c r="P15" s="12"/>
       <c r="Q15" s="12"/>
@@ -7237,21 +7232,21 @@
       <c r="A16" s="14">
         <v>5</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="95"/>
-      <c r="E16" s="95"/>
-      <c r="F16" s="95"/>
-      <c r="G16" s="95"/>
-      <c r="H16" s="95"/>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="84"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="83"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
@@ -7260,18 +7255,18 @@
       <c r="T16" s="12"/>
       <c r="U16" s="12"/>
       <c r="V16" s="12"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
-      <c r="Z16" s="84"/>
-      <c r="AA16" s="84"/>
-      <c r="AB16" s="84"/>
-      <c r="AC16" s="84"/>
-      <c r="AD16" s="84"/>
-      <c r="AE16" s="84"/>
-      <c r="AF16" s="84"/>
-      <c r="AG16" s="84"/>
-      <c r="AH16" s="84"/>
+      <c r="W16" s="83"/>
+      <c r="X16" s="83"/>
+      <c r="Y16" s="83"/>
+      <c r="Z16" s="83"/>
+      <c r="AA16" s="83"/>
+      <c r="AB16" s="83"/>
+      <c r="AC16" s="83"/>
+      <c r="AD16" s="83"/>
+      <c r="AE16" s="83"/>
+      <c r="AF16" s="83"/>
+      <c r="AG16" s="83"/>
+      <c r="AH16" s="83"/>
       <c r="AI16" s="12"/>
     </row>
     <row r="17" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -7299,18 +7294,18 @@
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
       <c r="V17" s="12"/>
-      <c r="W17" s="84"/>
-      <c r="X17" s="84"/>
-      <c r="Y17" s="84"/>
-      <c r="Z17" s="84"/>
-      <c r="AA17" s="84"/>
-      <c r="AB17" s="84"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="84"/>
+      <c r="W17" s="83"/>
+      <c r="X17" s="83"/>
+      <c r="Y17" s="83"/>
+      <c r="Z17" s="83"/>
+      <c r="AA17" s="83"/>
+      <c r="AB17" s="83"/>
+      <c r="AC17" s="83"/>
+      <c r="AD17" s="83"/>
+      <c r="AE17" s="83"/>
+      <c r="AF17" s="83"/>
+      <c r="AG17" s="83"/>
+      <c r="AH17" s="83"/>
       <c r="AI17" s="12"/>
     </row>
     <row r="18" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -7394,1172 +7389,1172 @@
       <c r="A1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="118" t="s">
+      <c r="M1" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
-      <c r="V1" s="118"/>
-      <c r="W1" s="118"/>
-      <c r="X1" s="118"/>
-      <c r="Y1" s="118"/>
-      <c r="Z1" s="118"/>
+      <c r="N1" s="117"/>
+      <c r="O1" s="117"/>
+      <c r="P1" s="117"/>
+      <c r="Q1" s="117"/>
+      <c r="R1" s="117"/>
+      <c r="S1" s="117"/>
+      <c r="T1" s="117"/>
+      <c r="U1" s="117"/>
+      <c r="V1" s="117"/>
+      <c r="W1" s="117"/>
+      <c r="X1" s="117"/>
+      <c r="Y1" s="117"/>
+      <c r="Z1" s="117"/>
       <c r="AM1" s="16" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="33.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="64"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="64"/>
+      <c r="AG2" s="64"/>
+      <c r="AH2" s="64"/>
+      <c r="AI2" s="64"/>
+      <c r="AJ2" s="64"/>
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="64"/>
+      <c r="AM2" s="64"/>
     </row>
     <row r="3" spans="1:39" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="Q3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="39" t="str">
+      <c r="Q3" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="54"/>
+      <c r="S3" s="54"/>
+      <c r="T3" s="54"/>
+      <c r="U3" s="65" t="str">
         <f>IF(活動報告書_記載例!W3="","",活動報告書_記載例!W3)</f>
         <v>鯖石保全会</v>
       </c>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="30" t="s">
+      <c r="V3" s="65"/>
+      <c r="W3" s="65"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="65"/>
+      <c r="Z3" s="65"/>
+      <c r="AA3" s="65"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="65"/>
+      <c r="AD3" s="65"/>
+      <c r="AE3" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="AF3" s="31"/>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="40">
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="58"/>
+      <c r="AJ3" s="66">
         <f>IF(活動報告書_記載例!A7="","",活動報告書_記載例!A7)</f>
         <v>46183</v>
       </c>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="67"/>
+      <c r="AM3" s="67"/>
     </row>
     <row r="4" spans="1:39" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="28" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="30" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="31"/>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="31"/>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
-      <c r="AH4" s="31"/>
-      <c r="AI4" s="32"/>
-      <c r="AJ4" s="111" t="s">
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="57"/>
+      <c r="AC4" s="57"/>
+      <c r="AD4" s="57"/>
+      <c r="AE4" s="57"/>
+      <c r="AF4" s="57"/>
+      <c r="AG4" s="57"/>
+      <c r="AH4" s="57"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="110" t="s">
         <v>22</v>
       </c>
-      <c r="AK4" s="111"/>
-      <c r="AL4" s="111"/>
-      <c r="AM4" s="111"/>
+      <c r="AK4" s="110"/>
+      <c r="AL4" s="110"/>
+      <c r="AM4" s="110"/>
     </row>
     <row r="5" spans="1:39" s="10" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
       <c r="F5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48" t="s">
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="112" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="50" t="s">
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="48" t="s">
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48" t="s">
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AD5" s="43"/>
-      <c r="AE5" s="43"/>
-      <c r="AF5" s="112" t="s">
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="AG5" s="113"/>
-      <c r="AH5" s="114"/>
-      <c r="AI5" s="115"/>
-      <c r="AJ5" s="111"/>
-      <c r="AK5" s="111"/>
-      <c r="AL5" s="111"/>
-      <c r="AM5" s="111"/>
+      <c r="AG5" s="112"/>
+      <c r="AH5" s="113"/>
+      <c r="AI5" s="114"/>
+      <c r="AJ5" s="110"/>
+      <c r="AK5" s="110"/>
+      <c r="AL5" s="110"/>
+      <c r="AM5" s="110"/>
     </row>
     <row r="6" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="2">
         <v>1</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="62">
         <v>2</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="28" t="s">
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="53">
+      <c r="K6" s="54"/>
+      <c r="L6" s="74">
         <v>1000</v>
       </c>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="108">
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="107">
         <f t="shared" ref="O6:O22" si="0">G6*L6</f>
         <v>2000</v>
       </c>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="110"/>
-      <c r="S6" s="33" t="s">
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="36">
+      <c r="T6" s="60"/>
+      <c r="U6" s="60"/>
+      <c r="V6" s="60"/>
+      <c r="W6" s="61"/>
+      <c r="X6" s="62">
         <v>2</v>
       </c>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="28" t="s">
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="37">
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="63">
         <v>900</v>
       </c>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="108">
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="107">
         <f t="shared" ref="AF6:AF22" si="1">X6*AC6</f>
         <v>1800</v>
       </c>
-      <c r="AG6" s="109"/>
-      <c r="AH6" s="109"/>
-      <c r="AI6" s="110"/>
-      <c r="AJ6" s="117">
+      <c r="AG6" s="108"/>
+      <c r="AH6" s="108"/>
+      <c r="AI6" s="109"/>
+      <c r="AJ6" s="116">
         <f>O6+AF6</f>
         <v>3800</v>
       </c>
-      <c r="AK6" s="117"/>
-      <c r="AL6" s="117"/>
-      <c r="AM6" s="117"/>
+      <c r="AK6" s="116"/>
+      <c r="AL6" s="116"/>
+      <c r="AM6" s="116"/>
     </row>
     <row r="7" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="62">
         <v>2</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="28" t="s">
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="53">
+      <c r="K7" s="54"/>
+      <c r="L7" s="74">
         <v>1000</v>
       </c>
-      <c r="M7" s="53"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="108">
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="107">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="30"/>
-      <c r="T7" s="31"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="31"/>
-      <c r="W7" s="32"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="108">
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="109"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="57"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="58"/>
+      <c r="X7" s="54"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="54"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="63"/>
+      <c r="AD7" s="63"/>
+      <c r="AE7" s="63"/>
+      <c r="AF7" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG7" s="109"/>
-      <c r="AH7" s="109"/>
-      <c r="AI7" s="110"/>
-      <c r="AJ7" s="117">
+      <c r="AG7" s="108"/>
+      <c r="AH7" s="108"/>
+      <c r="AI7" s="109"/>
+      <c r="AJ7" s="116">
         <f t="shared" ref="AJ7:AJ22" si="2">O7+AF7</f>
         <v>2000</v>
       </c>
-      <c r="AK7" s="117"/>
-      <c r="AL7" s="117"/>
-      <c r="AM7" s="117"/>
+      <c r="AK7" s="116"/>
+      <c r="AL7" s="116"/>
+      <c r="AM7" s="116"/>
     </row>
     <row r="8" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="62">
         <v>2</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="28" t="s">
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="28"/>
-      <c r="L8" s="53">
+      <c r="K8" s="54"/>
+      <c r="L8" s="74">
         <v>1000</v>
       </c>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="108">
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="107">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P8" s="109"/>
-      <c r="Q8" s="109"/>
-      <c r="R8" s="110"/>
-      <c r="S8" s="55" t="s">
+      <c r="P8" s="108"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="36">
+      <c r="T8" s="77"/>
+      <c r="U8" s="77"/>
+      <c r="V8" s="77"/>
+      <c r="W8" s="78"/>
+      <c r="X8" s="62">
         <v>1</v>
       </c>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="36"/>
-      <c r="AA8" s="28" t="s">
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="54">
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="75">
         <v>1000</v>
       </c>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="54"/>
-      <c r="AF8" s="108">
+      <c r="AD8" s="75"/>
+      <c r="AE8" s="75"/>
+      <c r="AF8" s="107">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="AG8" s="109"/>
-      <c r="AH8" s="109"/>
-      <c r="AI8" s="110"/>
-      <c r="AJ8" s="117">
+      <c r="AG8" s="108"/>
+      <c r="AH8" s="108"/>
+      <c r="AI8" s="109"/>
+      <c r="AJ8" s="116">
         <f t="shared" si="2"/>
         <v>3000</v>
       </c>
-      <c r="AK8" s="117"/>
-      <c r="AL8" s="117"/>
-      <c r="AM8" s="117"/>
+      <c r="AK8" s="116"/>
+      <c r="AL8" s="116"/>
+      <c r="AM8" s="116"/>
     </row>
     <row r="9" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
       <c r="F9" s="2">
         <v>8</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="62">
         <v>2</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="28" t="s">
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="28"/>
-      <c r="L9" s="53">
+      <c r="K9" s="54"/>
+      <c r="L9" s="74">
         <v>1000</v>
       </c>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="108">
+      <c r="M9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="107">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="28"/>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="28"/>
-      <c r="AD9" s="28"/>
-      <c r="AE9" s="28"/>
-      <c r="AF9" s="108">
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="109"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="54"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="54"/>
+      <c r="AA9" s="54"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="54"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG9" s="109"/>
-      <c r="AH9" s="109"/>
-      <c r="AI9" s="110"/>
-      <c r="AJ9" s="117">
+      <c r="AG9" s="108"/>
+      <c r="AH9" s="108"/>
+      <c r="AI9" s="109"/>
+      <c r="AJ9" s="116">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
-      <c r="AM9" s="117"/>
+      <c r="AK9" s="116"/>
+      <c r="AL9" s="116"/>
+      <c r="AM9" s="116"/>
     </row>
     <row r="10" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="108">
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P10" s="109"/>
-      <c r="Q10" s="109"/>
-      <c r="R10" s="110"/>
-      <c r="S10" s="30"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="28"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="28"/>
-      <c r="AE10" s="28"/>
-      <c r="AF10" s="108">
+      <c r="P10" s="108"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="109"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="57"/>
+      <c r="W10" s="58"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="54"/>
+      <c r="AB10" s="54"/>
+      <c r="AC10" s="54"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG10" s="109"/>
-      <c r="AH10" s="109"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="117">
+      <c r="AG10" s="108"/>
+      <c r="AH10" s="108"/>
+      <c r="AI10" s="109"/>
+      <c r="AJ10" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="117"/>
-      <c r="AL10" s="117"/>
-      <c r="AM10" s="117"/>
+      <c r="AK10" s="116"/>
+      <c r="AL10" s="116"/>
+      <c r="AM10" s="116"/>
     </row>
     <row r="11" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="108">
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="109"/>
-      <c r="Q11" s="109"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="31"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="31"/>
-      <c r="W11" s="32"/>
-      <c r="X11" s="28"/>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="28"/>
-      <c r="AB11" s="28"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="28"/>
-      <c r="AE11" s="28"/>
-      <c r="AF11" s="108">
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="109"/>
-      <c r="AH11" s="109"/>
-      <c r="AI11" s="110"/>
-      <c r="AJ11" s="117">
+      <c r="AG11" s="108"/>
+      <c r="AH11" s="108"/>
+      <c r="AI11" s="109"/>
+      <c r="AJ11" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="117"/>
-      <c r="AL11" s="117"/>
-      <c r="AM11" s="117"/>
+      <c r="AK11" s="116"/>
+      <c r="AL11" s="116"/>
+      <c r="AM11" s="116"/>
     </row>
     <row r="12" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="108">
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="109"/>
-      <c r="Q12" s="109"/>
-      <c r="R12" s="110"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="31"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="31"/>
-      <c r="W12" s="32"/>
-      <c r="X12" s="28"/>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="28"/>
-      <c r="AE12" s="28"/>
-      <c r="AF12" s="108">
+      <c r="P12" s="108"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="109"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG12" s="109"/>
-      <c r="AH12" s="109"/>
-      <c r="AI12" s="110"/>
-      <c r="AJ12" s="117">
+      <c r="AG12" s="108"/>
+      <c r="AH12" s="108"/>
+      <c r="AI12" s="109"/>
+      <c r="AJ12" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="117"/>
-      <c r="AL12" s="117"/>
-      <c r="AM12" s="117"/>
+      <c r="AK12" s="116"/>
+      <c r="AL12" s="116"/>
+      <c r="AM12" s="116"/>
     </row>
     <row r="13" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="108">
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="110"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AE13" s="28"/>
-      <c r="AF13" s="108">
+      <c r="P13" s="108"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="109"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="54"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="54"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="54"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG13" s="109"/>
-      <c r="AH13" s="109"/>
-      <c r="AI13" s="110"/>
-      <c r="AJ13" s="117">
+      <c r="AG13" s="108"/>
+      <c r="AH13" s="108"/>
+      <c r="AI13" s="109"/>
+      <c r="AJ13" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK13" s="117"/>
-      <c r="AL13" s="117"/>
-      <c r="AM13" s="117"/>
+      <c r="AK13" s="116"/>
+      <c r="AL13" s="116"/>
+      <c r="AM13" s="116"/>
     </row>
     <row r="14" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="108">
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="109"/>
-      <c r="Q14" s="109"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="31"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="31"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="28"/>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="28"/>
-      <c r="AB14" s="28"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="28"/>
-      <c r="AE14" s="28"/>
-      <c r="AF14" s="108">
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+      <c r="R14" s="109"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="54"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="54"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="54"/>
+      <c r="AF14" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG14" s="109"/>
-      <c r="AH14" s="109"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="117">
+      <c r="AG14" s="108"/>
+      <c r="AH14" s="108"/>
+      <c r="AI14" s="109"/>
+      <c r="AJ14" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK14" s="117"/>
-      <c r="AL14" s="117"/>
-      <c r="AM14" s="117"/>
+      <c r="AK14" s="116"/>
+      <c r="AL14" s="116"/>
+      <c r="AM14" s="116"/>
     </row>
     <row r="15" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="108">
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="31"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="31"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="108">
+      <c r="P15" s="108"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="109"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="58"/>
+      <c r="X15" s="54"/>
+      <c r="Y15" s="54"/>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="54"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="54"/>
+      <c r="AF15" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG15" s="109"/>
-      <c r="AH15" s="109"/>
-      <c r="AI15" s="110"/>
-      <c r="AJ15" s="117">
+      <c r="AG15" s="108"/>
+      <c r="AH15" s="108"/>
+      <c r="AI15" s="109"/>
+      <c r="AJ15" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK15" s="117"/>
-      <c r="AL15" s="117"/>
-      <c r="AM15" s="117"/>
+      <c r="AK15" s="116"/>
+      <c r="AL15" s="116"/>
+      <c r="AM15" s="116"/>
     </row>
     <row r="16" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="108">
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="109"/>
-      <c r="Q16" s="109"/>
-      <c r="R16" s="110"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28"/>
-      <c r="AB16" s="28"/>
-      <c r="AC16" s="28"/>
-      <c r="AD16" s="28"/>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="108">
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+      <c r="R16" s="109"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="58"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="54"/>
+      <c r="AF16" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG16" s="109"/>
-      <c r="AH16" s="109"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="117">
+      <c r="AG16" s="108"/>
+      <c r="AH16" s="108"/>
+      <c r="AI16" s="109"/>
+      <c r="AJ16" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK16" s="117"/>
-      <c r="AL16" s="117"/>
-      <c r="AM16" s="117"/>
+      <c r="AK16" s="116"/>
+      <c r="AL16" s="116"/>
+      <c r="AM16" s="116"/>
     </row>
     <row r="17" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="108">
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="54"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P17" s="109"/>
-      <c r="Q17" s="109"/>
-      <c r="R17" s="110"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="28"/>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28"/>
-      <c r="AB17" s="28"/>
-      <c r="AC17" s="28"/>
-      <c r="AD17" s="28"/>
-      <c r="AE17" s="28"/>
-      <c r="AF17" s="108">
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="109"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="54"/>
+      <c r="Y17" s="54"/>
+      <c r="Z17" s="54"/>
+      <c r="AA17" s="54"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="54"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG17" s="109"/>
-      <c r="AH17" s="109"/>
-      <c r="AI17" s="110"/>
-      <c r="AJ17" s="117">
+      <c r="AG17" s="108"/>
+      <c r="AH17" s="108"/>
+      <c r="AI17" s="109"/>
+      <c r="AJ17" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK17" s="117"/>
-      <c r="AL17" s="117"/>
-      <c r="AM17" s="117"/>
+      <c r="AK17" s="116"/>
+      <c r="AL17" s="116"/>
+      <c r="AM17" s="116"/>
     </row>
     <row r="18" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="108">
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="31"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="31"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="28"/>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28"/>
-      <c r="AB18" s="28"/>
-      <c r="AC18" s="28"/>
-      <c r="AD18" s="28"/>
-      <c r="AE18" s="28"/>
-      <c r="AF18" s="108">
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+      <c r="R18" s="109"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="57"/>
+      <c r="W18" s="58"/>
+      <c r="X18" s="54"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54"/>
+      <c r="AF18" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG18" s="109"/>
-      <c r="AH18" s="109"/>
-      <c r="AI18" s="110"/>
-      <c r="AJ18" s="117">
+      <c r="AG18" s="108"/>
+      <c r="AH18" s="108"/>
+      <c r="AI18" s="109"/>
+      <c r="AJ18" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK18" s="117"/>
-      <c r="AL18" s="117"/>
-      <c r="AM18" s="117"/>
+      <c r="AK18" s="116"/>
+      <c r="AL18" s="116"/>
+      <c r="AM18" s="116"/>
     </row>
     <row r="19" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="108">
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="31"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="31"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="28"/>
-      <c r="AF19" s="108">
+      <c r="P19" s="108"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="109"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="54"/>
+      <c r="Y19" s="54"/>
+      <c r="Z19" s="54"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="54"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG19" s="109"/>
-      <c r="AH19" s="109"/>
-      <c r="AI19" s="110"/>
-      <c r="AJ19" s="117">
+      <c r="AG19" s="108"/>
+      <c r="AH19" s="108"/>
+      <c r="AI19" s="109"/>
+      <c r="AJ19" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK19" s="117"/>
-      <c r="AL19" s="117"/>
-      <c r="AM19" s="117"/>
+      <c r="AK19" s="116"/>
+      <c r="AL19" s="116"/>
+      <c r="AM19" s="116"/>
     </row>
     <row r="20" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="108">
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="109"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AE20" s="28"/>
-      <c r="AF20" s="108">
+      <c r="P20" s="108"/>
+      <c r="Q20" s="108"/>
+      <c r="R20" s="109"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="54"/>
+      <c r="Y20" s="54"/>
+      <c r="Z20" s="54"/>
+      <c r="AA20" s="54"/>
+      <c r="AB20" s="54"/>
+      <c r="AC20" s="54"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="54"/>
+      <c r="AF20" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG20" s="109"/>
-      <c r="AH20" s="109"/>
-      <c r="AI20" s="110"/>
-      <c r="AJ20" s="117">
+      <c r="AG20" s="108"/>
+      <c r="AH20" s="108"/>
+      <c r="AI20" s="109"/>
+      <c r="AJ20" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK20" s="117"/>
-      <c r="AL20" s="117"/>
-      <c r="AM20" s="117"/>
+      <c r="AK20" s="116"/>
+      <c r="AL20" s="116"/>
+      <c r="AM20" s="116"/>
     </row>
     <row r="21" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="108">
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="110"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="31"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="31"/>
-      <c r="W21" s="32"/>
-      <c r="X21" s="28"/>
-      <c r="Y21" s="28"/>
-      <c r="Z21" s="28"/>
-      <c r="AA21" s="28"/>
-      <c r="AB21" s="28"/>
-      <c r="AC21" s="28"/>
-      <c r="AD21" s="28"/>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="108">
+      <c r="P21" s="108"/>
+      <c r="Q21" s="108"/>
+      <c r="R21" s="109"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="54"/>
+      <c r="Y21" s="54"/>
+      <c r="Z21" s="54"/>
+      <c r="AA21" s="54"/>
+      <c r="AB21" s="54"/>
+      <c r="AC21" s="54"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="54"/>
+      <c r="AF21" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG21" s="109"/>
-      <c r="AH21" s="109"/>
-      <c r="AI21" s="110"/>
-      <c r="AJ21" s="117">
+      <c r="AG21" s="108"/>
+      <c r="AH21" s="108"/>
+      <c r="AI21" s="109"/>
+      <c r="AJ21" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK21" s="117"/>
-      <c r="AL21" s="117"/>
-      <c r="AM21" s="117"/>
+      <c r="AK21" s="116"/>
+      <c r="AL21" s="116"/>
+      <c r="AM21" s="116"/>
     </row>
     <row r="22" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="108">
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="109"/>
-      <c r="R22" s="110"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="31"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="31"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="28"/>
-      <c r="AE22" s="28"/>
-      <c r="AF22" s="108">
+      <c r="P22" s="108"/>
+      <c r="Q22" s="108"/>
+      <c r="R22" s="109"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="54"/>
+      <c r="AA22" s="54"/>
+      <c r="AB22" s="54"/>
+      <c r="AC22" s="54"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="54"/>
+      <c r="AF22" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AG22" s="109"/>
-      <c r="AH22" s="109"/>
-      <c r="AI22" s="110"/>
-      <c r="AJ22" s="117">
+      <c r="AG22" s="108"/>
+      <c r="AH22" s="108"/>
+      <c r="AI22" s="109"/>
+      <c r="AJ22" s="116">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK22" s="117"/>
-      <c r="AL22" s="117"/>
-      <c r="AM22" s="117"/>
+      <c r="AK22" s="116"/>
+      <c r="AL22" s="116"/>
+      <c r="AM22" s="116"/>
     </row>
     <row r="23" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="36">
+      <c r="G23" s="62">
         <f>SUM(G6:G22)</f>
         <v>8</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="119">
+      <c r="H23" s="62"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="118">
         <f>SUM(O6:O22)</f>
         <v>8000</v>
       </c>
-      <c r="P23" s="120"/>
-      <c r="Q23" s="120"/>
-      <c r="R23" s="121"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="32"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="119">
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="120"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="118">
         <f>SUM(AF6:AF22)</f>
         <v>2800</v>
       </c>
-      <c r="AG23" s="120"/>
-      <c r="AH23" s="120"/>
-      <c r="AI23" s="121"/>
-      <c r="AJ23" s="119">
+      <c r="AG23" s="119"/>
+      <c r="AH23" s="119"/>
+      <c r="AI23" s="120"/>
+      <c r="AJ23" s="118">
         <f>SUM(AJ6:AJ22)</f>
         <v>10800</v>
       </c>
-      <c r="AK23" s="120"/>
-      <c r="AL23" s="120"/>
-      <c r="AM23" s="121"/>
+      <c r="AK23" s="119"/>
+      <c r="AL23" s="119"/>
+      <c r="AM23" s="120"/>
     </row>
     <row r="24" spans="1:39" ht="19.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="9" t="s">
